--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Workspace\SLUDI\MVP\Training\MaterData\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397A569D-0ACD-4E66-B787-C43A33F4A2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF1B1D7-ACA0-4EDD-AA60-D55568D5A261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4008" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4385,689 +4385,691 @@
   </si>
   <si>
     <t>{
-	"identity": [
-		{
-			"id": "IDSchemaVersion",
-			"description": "ID Schema Version",
-			"type": "number",
-			"controlType": null,
-			"fieldType": "default",
-			"inputRequired": false,
-			"validators": [],
-			"required": true
-		},
-		{
-			"id": "familyName",
-			"description": "Family Name",
-			"labelName": {
-				"eng": "Family Name",
-				"sin": "පෙළපත් නාමය",
-				"tam": "குடும்பப் பெயர்"
+	"identity": {
+		"identity": [
+			{
+				"id": "IDSchemaVersion",
+				"description": "ID Schema Version",
+				"type": "number",
+				"controlType": null,
+				"fieldType": "default",
+				"inputRequired": false,
+				"validators": [],
+				"required": true
 			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{3,50})$",
-					"arguments": []
-				}
+			{
+				"id": "familyName",
+				"description": "Family Name",
+				"labelName": {
+					"eng": "Family Name",
+					"sin": "පෙළපත් නාමය",
+					"tam": "குடும்பப் பெயர்"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{3,50})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": true,
+				"alignmentGroup": "Name"
+			},
+			{
+				"id": "name",
+				"description": "Name",
+				"labelName": {
+					"eng": "Name",
+					"sin": "නම",
+					"tam": "பெயர்"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{3,50}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": true,
+				"alignmentGroup": "Name"
+			},
+			{
+				"id": "surname",
+				"description": "Surname",
+				"labelName": {
+					"eng": "Surname",
+					"sin": "වාසගම",
+					"tam": "குடும்பப்பெயர்"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{3,50}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": true,
+				"alignmentGroup": "Name"
+			},
+			{
+				"id": "gender",
+				"description": "gender",
+				"labelName": {
+					"eng": "Gender",
+					"sin": "ස්ත්‍රී පුරුෂ භාවය",
+					"tam": "பாலினம்"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "dynamic",
+				"type": "simpleType",
+				"validators": [],
+				"required": true,
+				"transliteration": false,
+				"subType": "gender",
+				"alignmentGroup": "Demographics"
+			},
+			{
+				"id": "dateOfBirth",
+				"description": "dateOfBirth",
+				"labelName": {
+					"eng": "Date of Birth",
+					"sin": "උපන් දිනය",
+					"tam": "பிறந்த தேதி"
+				},
+				"controlType": "ageDate",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "string",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": false,
+				"alignmentGroup": "Demographics"
+			},
+			{
+				"id": "placeOfBirth",
+				"description": "placeOfBirth",
+				"labelName": {
+					"eng": "Place of Birth",
+					"sin": "උපන් ස්ථානය",
+					"tam": "பிறந்த இடம்"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{2,128}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": true,
+				"alignmentGroup": "Demographics"
+			},
+			{
+				"id": "divisionalSecretariatOfBirth",
+				"description": "divisionalSecretariatOfBirth",
+				"labelName": {
+					"eng": "Divisional Secretariat of Birth",
+					"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+					"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{1,50}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": true,
+				"alignmentGroup": "Demographics"
+			},
+			{
+				"id": "referenceIdentityNumber",
+				"description": "referenceIdentityNumber",
+				"labelName": {
+					"eng": "Existing National ID Number",
+					"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
+					"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "string",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Identifiers"
+			},
+			{
+				"id": "addressLine1",
+				"description": "addressLine1",
+				"labelName": {
+					"eng": "Address Line 1",
+					"sin": "පළමු ලිපින පේළිය",
+					"tam": "முகவரி வரி 1"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{1,128}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": true,
+				"alignmentGroup": "Permanent Address"
+			},
+			{
+				"id": "addressLine2",
+				"description": "addressLine2",
+				"labelName": {
+					"eng": "Address Line 2",
+					"sin": "දෙවන ලිපින පේළිය",
+					"tam": "முகவரி வரி 2"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,128})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": true,
+				"alignmentGroup": "Permanent Address"
+			},
+			{
+				"id": "addressLine3",
+				"description": "addressLine3",
+				"labelName": {
+					"eng": "Address Line 3",
+					"sin": "තෙවන ලිපින පේළිය",
+					"tam": "முகவரி வரி 3"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,128})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": true,
+				"alignmentGroup": "Permanent Address"
+			},
+			{
+				"id": "province",
+				"description": "province",
+				"labelName": {
+					"eng": "Province",
+					"sin": "පළාත",
+					"tam": "மாகாணம்"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{1,50}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": false,
+				"alignmentGroup": "Permanent Address",
+				"locationHierarchyLevel": 1,
+				"parentLocCode": "LKA"
+			},
+			{
+				"id": "district",
+				"description": "district",
+				"labelName": {
+					"eng": "District",
+					"sin": "දිස්ත්‍රික්කය",
+					"tam": "மாவட்டம்"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{1,50}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": false,
+				"alignmentGroup": "Permanent Address",
+				"locationHierarchyLevel": 2
+			},
+			{
+				"id": "divisionalSecretariat",
+				"description": "divisionalSecretariat",
+				"labelName": {
+					"eng": "Divisional Secretariat Division",
+					"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+					"tam": "பிரதேச செயலகப் பிரிவு"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{1,50}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": false,
+				"alignmentGroup": "Permanent Address",
+				"locationHierarchyLevel": 3
+			},
+			{
+				"id": "grammaNiladhari",
+				"description": "grammaNiladhari",
+				"labelName": {
+					"eng": "Grama Niladhari Division",
+					"sin": "ග්‍රාම නිලධාරී වසම",
+					"tam": "கிராம அலுவலர் பிரிவு"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(?=.{1,50}$).*",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": false,
+				"alignmentGroup": "Permanent Address",
+				"locationHierarchyLevel": 4
+			},
+			{
+				"id": "postalCode",
+				"description": "postalCode",
+				"labelName": {
+					"eng": "Postal Code",
+					"sin": "තැපැල් කේතය",
+					"tam": "அஞ்சல் குறியீடு"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "string",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^[0-9]{5}$",
+						"arguments": []
+					}
+				],
+				"required": true,
+				"transliteration": false,
+				"alignmentGroup": "Permanent Address"
+			},
+			{
+				"id": "currentAddressLine1",
+				"description": "currentAddressLine1",
+				"labelName": {
+					"eng": "Address Line 1",
+					"sin": "පළමු ලිපින පේළිය",
+					"tam": "முகவரி வரி 1"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,128})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": true,
+				"alignmentGroup": "Current Address"
+			},
+			{
+				"id": "currentAddressLine2",
+				"description": "currentAddressLine2",
+				"labelName": {
+					"eng": "Address Line 2",
+					"sin": "දෙවන ලිපින පේළිය",
+					"tam": "முகவரி வரி 2"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,128})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": true,
+				"alignmentGroup": "Current Address"
+			},
+			{
+				"id": "currentAddressLine3",
+				"description": "currentAddressLine3",
+				"labelName": {
+					"eng": "Address Line 3",
+					"sin": "තෙවන ලිපින පේළිය",
+					"tam": "முகவரி வரி 3"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,128})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": true,
+				"alignmentGroup": "Current Address"
+			},
+			{
+				"id": "currentProvince",
+				"description": "currentProvince",
+				"labelName": {
+					"eng": "Province",
+					"sin": "පළාත",
+					"tam": "மாகாணம்"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,50})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Current Address",
+				"locationHierarchyLevel": 1,
+				"parentLocCode": "LKA"
+			},
+			{
+				"id": "currentDistrict",
+				"description": "currentDistrict",
+				"labelName": {
+					"eng": "District",
+					"sin": "දිස්ත්‍රික්කය",
+					"tam": "மாவட்டம்"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,50})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Current Address",
+				"locationHierarchyLevel": 2
+			},
+			{
+				"id": "currentDivisionalSecretariat",
+				"description": "currentDivisionalSecretariat",
+				"labelName": {
+					"eng": "Divisional Secretariat Division",
+					"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+					"tam": "பிரதேச செயலகப் பிரிவு"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,50})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Current Address",
+				"locationHierarchyLevel": 3
+			},
+			{
+				"id": "currentGramaNiladhari",
+				"description": "currentGramaNiladhari",
+				"labelName": {
+					"eng": "Grama Niladhari Division",
+					"sin": "ග්‍රාම නිලධාරී වසම",
+					"tam": "கிராம அலுவலர் பிரிவு"
+				},
+				"controlType": "dropdown",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "simpleType",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(|.{1,50})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Current Address",
+				"locationHierarchyLevel": 4
+			},
+			{
+				"id": "currentPostalCode",
+				"description": "currentPostalCode",
+				"labelName": {
+					"eng": "Current Postal Code",
+					"sin": "වර්තමාන තැපැල් කේතය",
+					"tam": "தற்போதைய அஞ்சல் குறியீடு"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "string",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^$|^[0-9]{5}$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Current Address"
+			},
+			{
+				"id": "phone",
+				"description": "phone",
+				"labelName": {
+					"eng": "Phone",
+					"sin": "දුරකථන අංකය",
+					"tam": "தொலைபேசி"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "string",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^(0?7[0-9]{8})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Contact"
+			},
+			{
+				"id": "email",
+				"description": "email",
+				"labelName": {
+					"eng": "Email",
+					"sin": "විද්‍යුත් තැපෑල",
+					"tam": "மின்னஞ்சல்"
+				},
+				"controlType": "textbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "string",
+				"validators": [
+					{
+						"type": "regex",
+						"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
+						"arguments": []
+					}
+				],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Contact"
+			},
+			{
+				"id": "proofOfAddress",
+				"description": "proofOfAddress",
+				"labelName": {
+					"eng": "Address Proof",
+					"sin": "පදිංචිය තහවුරු කිරීමේ සහතිකය",
+					"tam": "முகவரி சான்று"
+				},
+				"controlType": "fileupload",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "documentType",
+				"validators": [],
+				"required": false,
+				"transliteration": false,
+				"subType": "POA",
+				"alignmentGroup": "Documents"
+			},
+			{
+				"id": "proofOfIdentity",
+				"description": "proofOfIdentity",
+				"labelName": {
+					"eng": "Identity Proof",
+					"sin": "අනන්‍යතා තහවුරු කිරීමේ සහතිකය",
+					"tam": "அடையாளச் சான்று"
+				},
+				"controlType": "fileupload",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "documentType",
+				"validators": [],
+				"required": false,
+				"transliteration": false,
+				"subType": "POI",
+				"alignmentGroup": "Documents"
+			},
+			{
+				"id": "proofOfDateOfBirth",
+				"description": "proofOfDateOfBirth",
+				"labelName": {
+					"eng": "Date of Birth Proof",
+					"sin": "උප්පැන්න සහතිකය",
+					"tam": "பிறந்த தேதிச் சான்று"
+				},
+				"controlType": "fileupload",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "documentType",
+				"validators": [],
+				"required": false,
+				"transliteration": false,
+				"subType": "POB",
+				"alignmentGroup": "Documents"
+			}
+		],
+		"locationHierarchy": [
+			[
+				"province",
+				"district",
+				"divisionalSecretariat",
+				"grammaNiladhari"
 			],
-			"required": false,
-			"transliteration": true,
-			"alignmentGroup": "Name"
-		},
-		{
-			"id": "name",
-			"description": "Name",
-			"labelName": {
-				"eng": "Name",
-				"sin": "නම",
-				"tam": "பெயர்"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{3,50}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": true,
-			"alignmentGroup": "Name"
-		},
-		{
-			"id": "surname",
-			"description": "Surname",
-			"labelName": {
-				"eng": "Surname",
-				"sin": "වාසගම",
-				"tam": "குடும்பப்பெயர்"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{3,50}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": true,
-			"alignmentGroup": "Name"
-		},
-		{
-			"id": "gender",
-			"description": "gender",
-			"labelName": {
-				"eng": "Gender",
-				"sin": "ස්ත්‍රී පුරුෂ භාවය",
-				"tam": "பாலினம்"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "dynamic",
-			"type": "simpleType",
-			"validators": [],
-			"required": true,
-			"transliteration": false,
-			"subType": "gender",
-			"alignmentGroup": "Demographics"
-		},
-		{
-			"id": "dateOfBirth",
-			"description": "dateOfBirth",
-			"labelName": {
-				"eng": "Date of Birth",
-				"sin": "උපන් දිනය",
-				"tam": "பிறந்த தேதி"
-			},
-			"controlType": "ageDate",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "string",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": false,
-			"alignmentGroup": "Demographics"
-		},
-		{
-			"id": "placeOfBirth",
-			"description": "placeOfBirth",
-			"labelName": {
-				"eng": "Place of Birth",
-				"sin": "උපන් ස්ථානය",
-				"tam": "பிறந்த இடம்"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{2,128}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": true,
-			"alignmentGroup": "Demographics"
-		},
-		{
-			"id": "divisionalSecretariatOfBirth",
-			"description": "divisionalSecretariatOfBirth",
-			"labelName": {
-				"eng": "Divisional Secretariat of Birth",
-				"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-				"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{1,50}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": true,
-			"alignmentGroup": "Demographics"
-		},
-		{
-			"id": "referenceIdentityNumber",
-			"description": "referenceIdentityNumber",
-			"labelName": {
-				"eng": "Existing National ID Number",
-				"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
-				"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "string",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Identifiers"
-		},
-		{
-			"id": "addressLine1",
-			"description": "addressLine1",
-			"labelName": {
-				"eng": "Address Line 1",
-				"sin": "පළමු ලිපින පේළිය",
-				"tam": "முகவரி வரி 1"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{1,128}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": true,
-			"alignmentGroup": "Permanent Address"
-		},
-		{
-			"id": "addressLine2",
-			"description": "addressLine2",
-			"labelName": {
-				"eng": "Address Line 2",
-				"sin": "දෙවන ලිපින පේළිය",
-				"tam": "முகவரி வரி 2"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,128})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": true,
-			"alignmentGroup": "Permanent Address"
-		},
-		{
-			"id": "addressLine3",
-			"description": "addressLine3",
-			"labelName": {
-				"eng": "Address Line 3",
-				"sin": "තෙවන ලිපින පේළිය",
-				"tam": "முகவரி வரி 3"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,128})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": true,
-			"alignmentGroup": "Permanent Address"
-		},
-		{
-			"id": "province",
-			"description": "province",
-			"labelName": {
-				"eng": "Province",
-				"sin": "පළාත",
-				"tam": "மாகாணம்"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{1,50}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": false,
-			"alignmentGroup": "Permanent Address",
-			"locationHierarchyLevel": 1,
-			"parentLocCode": "LKA"
-		},
-		{
-			"id": "district",
-			"description": "district",
-			"labelName": {
-				"eng": "District",
-				"sin": "දිස්ත්‍රික්කය",
-				"tam": "மாவட்டம்"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{1,50}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": false,
-			"alignmentGroup": "Permanent Address",
-			"locationHierarchyLevel": 2
-		},
-		{
-			"id": "divisionalSecretariat",
-			"description": "divisionalSecretariat",
-			"labelName": {
-				"eng": "Divisional Secretariat Division",
-				"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-				"tam": "பிரதேச செயலகப் பிரிவு"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{1,50}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": false,
-			"alignmentGroup": "Permanent Address",
-			"locationHierarchyLevel": 3
-		},
-		{
-			"id": "grammaNiladhari",
-			"description": "grammaNiladhari",
-			"labelName": {
-				"eng": "Grama Niladhari Division",
-				"sin": "ග්‍රාම නිලධාරී වසම",
-				"tam": "கிராம அலுவலர் பிரிவு"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(?=.{1,50}$).*",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": false,
-			"alignmentGroup": "Permanent Address",
-			"locationHierarchyLevel": 4
-		},
-		{
-			"id": "postalCode",
-			"description": "postalCode",
-			"labelName": {
-				"eng": "Postal Code",
-				"sin": "තැපැල් කේතය",
-				"tam": "அஞ்சல் குறியீடு"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "string",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^[0-9]{5}$",
-					"arguments": []
-				}
-			],
-			"required": true,
-			"transliteration": false,
-			"alignmentGroup": "Permanent Address"
-		},
-		{
-			"id": "currentAddressLine1",
-			"description": "currentAddressLine1",
-			"labelName": {
-				"eng": "Address Line 1",
-				"sin": "පළමු ලිපින පේළිය",
-				"tam": "முகவரி வரி 1"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,128})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": true,
-			"alignmentGroup": "Current Address"
-		},
-		{
-			"id": "currentAddressLine2",
-			"description": "currentAddressLine2",
-			"labelName": {
-				"eng": "Address Line 2",
-				"sin": "දෙවන ලිපින පේළිය",
-				"tam": "முகவரி வரி 2"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,128})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": true,
-			"alignmentGroup": "Current Address"
-		},
-		{
-			"id": "currentAddressLine3",
-			"description": "currentAddressLine3",
-			"labelName": {
-				"eng": "Address Line 3",
-				"sin": "තෙවන ලිපින පේළිය",
-				"tam": "முகவரி வரி 3"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,128})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": true,
-			"alignmentGroup": "Current Address"
-		},
-		{
-			"id": "currentProvince",
-			"description": "currentProvince",
-			"labelName": {
-				"eng": "Province",
-				"sin": "පළාත",
-				"tam": "மாகாணம்"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,50})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Current Address",
-			"locationHierarchyLevel": 1,
-			"parentLocCode": "LKA"
-		},
-		{
-			"id": "currentDistrict",
-			"description": "currentDistrict",
-			"labelName": {
-				"eng": "District",
-				"sin": "දිස්ත්‍රික්කය",
-				"tam": "மாவட்டம்"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,50})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Current Address",
-			"locationHierarchyLevel": 2
-		},
-		{
-			"id": "currentDivisionalSecretariat",
-			"description": "currentDivisionalSecretariat",
-			"labelName": {
-				"eng": "Divisional Secretariat Division",
-				"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-				"tam": "பிரதேச செயலகப் பிரிவு"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,50})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Current Address",
-			"locationHierarchyLevel": 3
-		},
-		{
-			"id": "currentGramaNiladhari",
-			"description": "currentGramaNiladhari",
-			"labelName": {
-				"eng": "Grama Niladhari Division",
-				"sin": "ග්‍රාම නිලධාරී වසම",
-				"tam": "கிராம அலுவலர் பிரிவு"
-			},
-			"controlType": "dropdown",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "simpleType",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(|.{1,50})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Current Address",
-			"locationHierarchyLevel": 4
-		},
-		{
-			"id": "currentPostalCode",
-			"description": "currentPostalCode",
-			"labelName": {
-				"eng": "Current Postal Code",
-				"sin": "වර්තමාන තැපැල් කේතය",
-				"tam": "தற்போதைய அஞ்சல் குறியீடு"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "string",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^$|^[0-9]{5}$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Current Address"
-		},
-		{
-			"id": "phone",
-			"description": "phone",
-			"labelName": {
-				"eng": "Phone",
-				"sin": "දුරකථන අංකය",
-				"tam": "தொலைபேசி"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "string",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^(0?7[0-9]{8})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Contact"
-		},
-		{
-			"id": "email",
-			"description": "email",
-			"labelName": {
-				"eng": "Email",
-				"sin": "විද්‍යුත් තැපෑල",
-				"tam": "மின்னஞ்சல்"
-			},
-			"controlType": "textbox",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "string",
-			"validators": [
-				{
-					"type": "regex",
-					"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
-					"arguments": []
-				}
-			],
-			"required": false,
-			"transliteration": false,
-			"alignmentGroup": "Contact"
-		},
-		{
-			"id": "proofOfAddress",
-			"description": "proofOfAddress",
-			"labelName": {
-				"eng": "Address Proof",
-				"sin": "පදිංචිය තහවුරු කිරීමේ සහතිකය",
-				"tam": "முகவரி சான்று"
-			},
-			"controlType": "fileupload",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "documentType",
-			"validators": [],
-			"required": false,
-			"transliteration": false,
-			"subType": "POA",
-			"alignmentGroup": "Documents"
-		},
-		{
-			"id": "proofOfIdentity",
-			"description": "proofOfIdentity",
-			"labelName": {
-				"eng": "Identity Proof",
-				"sin": "අනන්‍යතා තහවුරු කිරීමේ සහතිකය",
-				"tam": "அடையாளச் சான்று"
-			},
-			"controlType": "fileupload",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "documentType",
-			"validators": [],
-			"required": false,
-			"transliteration": false,
-			"subType": "POI",
-			"alignmentGroup": "Documents"
-		},
-		{
-			"id": "proofOfDateOfBirth",
-			"description": "proofOfDateOfBirth",
-			"labelName": {
-				"eng": "Date of Birth Proof",
-				"sin": "උප්පැන්න සහතිකය",
-				"tam": "பிறந்த தேதிச் சான்று"
-			},
-			"controlType": "fileupload",
-			"inputRequired": true,
-			"fieldType": "default",
-			"type": "documentType",
-			"validators": [],
-			"required": false,
-			"transliteration": false,
-			"subType": "POB",
-			"alignmentGroup": "Documents"
-		}
-	],
-	"locationHierarchy": [
-		[
-			"province",
-			"district",
-			"divisionalSecretariat",
-			"grammaNiladhari"
-		],
-		[
-			"currentProvince",
-			"currentDistrict",
-			"currentDivisionalSecretariat",
-			"currentGramaNiladhari"
+			[
+				"currentProvince",
+				"currentDistrict",
+				"currentDivisionalSecretariat",
+				"currentGramaNiladhari"
+			]
 		]
-	]
+	}
 }</t>
   </si>
 </sst>

--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Workspace\SLUDI\MVP\Training\MaterData\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\mosip-training\sludi-mvp-dev-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF1B1D7-ACA0-4EDD-AA60-D55568D5A261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017A40AF-3E26-46B8-89CF-C4707889C7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4008" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -169,3972 +169,6 @@
   </si>
   <si>
     <t>bioCorrectionProcess</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
-	"id": "NEW",
-	"order": 1,
-	"flow": "NEW",
-	"isSubProcess": false,
-	"label": {
-		"eng": "New Registration",
-		"sin": "නව ලියාපදිංචිය",
-		"tam": "புதிய பதிவு"
-	},
-	"screens": [
-		{
-			"order": 1,
-			"name": "consentdet",
-			"label": {
-				"eng": "Consent",
-				"sin": "එකඟතාව",
-				"tam": "இணக்கம்"
-			},
-			"caption": {
-				"eng": "Consent",
-				"sin": "එකඟතාව",
-				"tam": "இணக்கம்"
-			},
-			"fields": [
-				{
-					"id": "IDSchemaVersion",
-					"inputRequired": false,
-					"type": "number",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "ID Schema Version",
-					"label": {
-						"eng": "IDSchemaVersion",
-						"sin": "හැඳුනුම්පත් යෝජනා ක්‍රම අනුවාදය",
-						"tam": "அடையாளத் திட்டப் பதிப்பு"
-					},
-					"controlType": null,
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "none",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": null,
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "IdSchemaVersion"
-				},
-				{
-					"id": "consentText",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Consent",
-					"label": {},
-					"controlType": "html",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consentText",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": "Registration Consent",
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consentText"
-				},
-				{
-					"id": "consent",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "consent accepted",
-					"label": {
-						"eng": "I have read and accept terms and conditions to share my PII",
-						"sin": "මම මගේ පෞද්ගලික තොරතුරු බෙදා ගැනීමේ නියමයන් සහ කොන්දේසි කියවා එකඟ වෙමි",
-						"tam": "எனது தனிப்பட்ட தகவல்களைப் பகிர்வதற்கான நிபந்தனைகளைப் படித்து ஏற்றுக்கொள்கிறேன்"
-					},
-					"controlType": "checkbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consent",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consent"
-				},
-				{
-					"id": "preferredLang",
-					"inputRequired": false,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "user preferred Language",
-					"label": {
-						"eng": "Notification Language",
-						"sin": "දැනුම්දීමේ භාෂාව",
-						"tam": "அறிவிப்பு மொழி"
-					},
-					"controlType": "button",
-					"fieldType": "dynamic",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "group1",
-					"visible": null,
-					"contactType": null,
-					"group": "PreferredLanguage",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "preferredLang"
-				}
-			],
-			"layoutTemplate": null,
-			"preRegFetchRequired": false,
-			"active": false
-		},
-		{
-			"order": 2,
-			"name": "DemographicDetails",
-			"label": {
-				"eng": "Demographic Details",
-				"sin": "ජනවිකාස විස්තර",
-				"tam": "மக்கள்தொகை விவரங்கள்"
-			},
-			"caption": {
-				"eng": "Demographic Details",
-				"sin": "ජනවිකාස විස්තර",
-				"tam": "மக்கள்தொகை விவரங்கள்"
-			},
-			"fields": [
-				{
-					"id": "familyName",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Family Name",
-					"label": {
-						"eng": "Family Name",
-						"sin": "පෙළපත් නාමය",
-						"tam": "குடும்பப் பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{3,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "FamilyName",
-					"groupLabel": {
-						"eng": "Family Name",
-						"sin": "පෙළපත් නාමය",
-						"tam": "குடும்பப் பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "familyName"
-				},
-				{
-					"id": "name",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Name",
-					"label": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{3,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Name",
-					"groupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "name"
-				},
-				{
-					"id": "surname",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Surname",
-					"label": {
-						"eng": "Surname",
-						"sin": "වාසගම",
-						"tam": "குடும்பப்பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{3,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Surname",
-					"groupLabel": {
-						"eng": "Surname",
-						"sin": "වාසගම",
-						"tam": "குடும்பப்பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "surname"
-				},
-				{
-					"id": "gender",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "gender",
-					"label": {
-						"eng": "Gender",
-						"sin": "ස්ත්‍රී පුරුෂ භාවය",
-						"tam": "பாலினம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "dynamic",
-					"format": "",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Gender",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gender"
-				},
-				{
-					"id": "dateOfBirth",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "dateOfBirth",
-					"label": {
-						"eng": "DOB",
-						"sin": "උපන් දිනය",
-						"tam": "பிறந்த தேதி"
-					},
-					"controlType": "ageDate",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "DateOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "dateOfBirth"
-				},
-				{
-					"id": "placeOfBirth",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "placeOfBirth",
-					"label": {
-						"eng": "Place of Birth",
-						"sin": "උපන් ස්ථානය",
-						"tam": "பிறந்த இடம்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{2,128}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PlaceOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "placeOfBirth"
-				},
-				{
-					"id": "divisionalSecretariatOfBirth",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "divisionalSecretariatOfBirth",
-					"label": {
-						"eng": "Divisional Secretariat of Birth",
-						"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PlaceOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatOfBirth"
-				},
-				{
-					"id": "addressLine1",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine1",
-					"label": {
-						"eng": "Address Line 1",
-						"sin": "පළමු ලිපින පේළිය",
-						"tam": "முகவரி வரி 1"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,128}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine1"
-				},
-				{
-					"id": "addressLine2",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine2",
-					"label": {
-						"eng": "Address Line 2",
-						"sin": "දෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 2"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine2"
-				},
-				{
-					"id": "addressLine3",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine3",
-					"label": {
-						"eng": "Address Line 3",
-						"sin": "තෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 3"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine3"
-				},
-				{
-					"id": "province",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "province",
-					"label": {
-						"eng": "Province",
-						"sin": "පළාත",
-						"tam": "மாகாணம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": [
-						"province",
-						"district",
-						"divisionalSecretariat",
-						"grammaNiladhari"
-					],
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Province"
-				},
-				{
-					"id": "district",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "District",
-					"label": {
-						"eng": "District",
-						"sin": "දිස්ත්‍රික්කය",
-						"tam": "மாவட்டம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "District"
-				},
-				{
-					"id": "divisionalSecretariat",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Divisional Secretariat Division",
-					"label": {
-						"eng": "Divisional Secretariat Division",
-						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatDivision"
-				},
-				{
-					"id": "grammaNiladhari",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Grama Niladhari Division",
-					"label": {
-						"eng": "Grama Niladhari Division",
-						"sin": "ග්‍රාම නිලධාරී වසම",
-						"tam": "கிராம அலுவலர் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gramaNiladhariDivision"
-				},
-				{
-					"id": "postalCode",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "postalCode",
-					"label": {
-						"eng": "Postal Code",
-						"sin": "තැපැල් කේතය",
-						"tam": "அஞ்சல் குறியீடு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^[0-9]{5}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "postalCode"
-				},
-				{
-					"id": "currentAddressLine1",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine1",
-					"label": {
-						"eng": "Address Line 1",
-						"sin": "පළමු ලිපින පේළිය",
-						"tam": "முகவரி வரி 1"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine1"
-				},
-				{
-					"id": "currentAddressLine2",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine2",
-					"label": {
-						"eng": "Address Line 2",
-						"sin": "දෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 2"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine2"
-				},
-				{
-					"id": "currentAddressLine3",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine3",
-					"label": {
-						"eng": "Address Line 3",
-						"sin": "තෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 3"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine3"
-				},
-				{
-					"id": "currentProvince",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentProvince",
-					"label": {
-						"eng": "Province",
-						"sin": "පළාත",
-						"tam": "மாகாணம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": [
-						"currentProvince",
-						"currentDistrict",
-						"currentDivisionalSecretariat",
-						"currentGramaNiladhari"
-					],
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Province"
-				},
-				{
-					"id": "currentDistrict",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentDistrict",
-					"label": {
-						"eng": "District",
-						"sin": "දිස්ත්‍රික්කය",
-						"tam": "மாவட்டம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "District"
-				},
-				{
-					"id": "currentDivisionalSecretariat",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentDivisionalSecretariat",
-					"label": {
-						"eng": "Divisional Secretariat Division",
-						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatDivision"
-				},
-				{
-					"id": "currentGramaNiladhari",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentGramaNiladhari",
-					"label": {
-						"eng": "Grama Niladhari Division",
-						"sin": "ග්‍රාම නිලධාරී වසම",
-						"tam": "கிராம அலுவலர் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gramaNiladhariDivision"
-				},
-				{
-					"id": "currentPostalCode",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentPostalCode",
-					"label": {
-						"eng": "Current Postal Code",
-						"sin": "වර්තමාන තැපැල් කේතය",
-						"tam": "தற்போதைய அஞ்சல் குறியீடு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^$|^[0-9]{5}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentPostalCode"
-				},
-				{
-					"id": "referenceIdentityNumber",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "referenceIdentityNumber",
-					"label": {
-						"eng": "National ID Number",
-						"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
-						"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "kyc",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "ReferenceIdentityNumber",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "referenceIdentityNumber"
-				},
-				{
-					"id": "phone",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "phone",
-					"label": {
-						"eng": "Phone",
-						"sin": "දුරකථන අංකය",
-						"tam": "தொலைபேசி"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^7[0-9]{8}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Address",
-					"alignmentGroupLabel": {
-						"eng": "Address",
-						"sin": "ලිපිනය",
-						"tam": "முகவரி"
-					},
-					"visible": null,
-					"contactType": "email",
-					"group": "Phone",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Phone"
-				},
-				{
-					"id": "email",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "email",
-					"label": {
-	</t>
-  </si>
-  <si>
-    <t>{
-	"id": "UPDATE",
-	"order": 2,
-	"flow": "UPDATE",
-	"isSubProcess": false,
-	"label": {
-		"eng": "Update UIN",
-		"sin": "SLUDI අංකය යාවත්කාලීන කිරීම",
-		"tam": "SLUDI எண்ணைப் புதுப்பித்தல்"
-	},
-	"screens": [
-		{
-			"order": 1,
-			"name": "consentdet",
-			"label": {
-				"eng": "Consent",
-				"sin": "එකඟතාව",
-				"tam": "இணக்கம்"
-			},
-			"caption": {
-				"eng": "Consent",
-				"sin": "එකඟතාව",
-				"tam": "இணக்கம்"
-			},
-			"fields": [
-				{
-					"id": "IDSchemaVersion",
-					"inputRequired": false,
-					"type": "number",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "ID Schema Version",
-					"label": {
-						"eng": "IDSchemaVersion",
-						"sin": "හැඳුනුම්පත් යෝජනා ක්‍රම අනුවාදය",
-						"tam": "அடையாளத் திட்டப் பதிப்பு"
-					},
-					"controlType": null,
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "none",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": null,
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "IdSchemaVersion"
-				},
-				{
-					"id": "consentText",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Consent",
-					"label": {},
-					"controlType": "html",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consentText",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": "Registration Consent",
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consentText"
-				},
-				{
-					"id": "consent",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "consent accepted",
-					"label": {
-						"eng": "I have read and accept terms and conditions to share my PII",
-						"sin": "මම මගේ පෞද්ගලික තොරතුරු බෙදා ගැනීමේ නියමයන් සහ කොන්දේසි කියවා එකඟ වෙමි",
-						"tam": "எனது தனிப்பட்ட தகவல்களைப் பகிர்வதற்கான நிபந்தனைகளைப் படித்து ஏற்றுக்கொள்கிறேன்"
-					},
-					"controlType": "checkbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consent",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consent"
-				},
-				{
-					"id": "preferredLang",
-					"inputRequired": false,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "user preferred Language",
-					"label": {
-						"eng": "Notification Language",
-						"sin": "දැනුම්දීමේ භාෂාව",
-						"tam": "அறிவிப்பு மொழி"
-					},
-					"controlType": "button",
-					"fieldType": "dynamic",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "group1",
-					"visible": null,
-					"contactType": null,
-					"group": "PreferredLanguage",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "preferredLang"
-				}
-			],
-			"layoutTemplate": null,
-			"preRegFetchRequired": false,
-			"active": false
-		},
-		{
-			"order": 2,
-			"name": "DemographicDetails",
-			"label": {
-				"eng": "Demographic Details",
-				"sin": "ජනවිකාස විස්තර",
-				"tam": "மக்கள்தொகை விவரங்கள்"
-			},
-			"caption": {
-				"eng": "Demographic Details",
-				"sin": "ජනවිකාස විස්තර",
-				"tam": "மக்கள்தொகை விவரங்கள்"
-			},
-			"fields": [
-				{
-					"id": "familyName",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Family Name",
-					"label": {
-						"eng": "Family Name",
-						"sin": "පෙළපත් නාමය",
-						"tam": "குடும்பப் பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{3,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "FamilyName",
-					"groupLabel": {
-						"eng": "Family Name",
-						"sin": "පෙළපත් නාමය",
-						"tam": "குடும்பப் பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "familyName"
-				},
-				{
-					"id": "name",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Name",
-					"label": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{3,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Name",
-					"groupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "name"
-				},
-				{
-					"id": "surname",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Surname",
-					"label": {
-						"eng": "Surname",
-						"sin": "වාසගම",
-						"tam": "குடும்பப்பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{3,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Surname",
-					"groupLabel": {
-						"eng": "Surname",
-						"sin": "වාසගම",
-						"tam": "குடும்பப்பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "surname"
-				},
-				{
-					"id": "gender",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "gender",
-					"label": {
-						"eng": "Gender",
-						"sin": "ස්ත්‍රී පුරුෂ භාවය",
-						"tam": "பாலினம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "dynamic",
-					"format": "",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Gender",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gender"
-				},
-				{
-					"id": "dateOfBirth",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "dateOfBirth",
-					"label": {
-						"eng": "DOB",
-						"sin": "උපන් දිනය",
-						"tam": "பிறந்த தேதி"
-					},
-					"controlType": "ageDate",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "DateOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "dateOfBirth"
-				},
-				{
-					"id": "placeOfBirth",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "placeOfBirth",
-					"label": {
-						"eng": "Place of Birth",
-						"sin": "උපන් ස්ථානය",
-						"tam": "பிறந்த இடம்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{2,128}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PlaceOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "placeOfBirth"
-				},
-				{
-					"id": "divisionalSecretariatOfBirth",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "divisionalSecretariatOfBirth",
-					"label": {
-						"eng": "Divisional Secretariat of Birth",
-						"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PlaceOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatOfBirth"
-				},
-				{
-					"id": "addressLine1",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine1",
-					"label": {
-						"eng": "Address Line 1",
-						"sin": "පළමු ලිපින පේළිය",
-						"tam": "முகவரி வரி 1"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,128}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine1"
-				},
-				{
-					"id": "addressLine2",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine2",
-					"label": {
-						"eng": "Address Line 2",
-						"sin": "දෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 2"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine2"
-				},
-				{
-					"id": "addressLine3",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine3",
-					"label": {
-						"eng": "Address Line 3",
-						"sin": "තෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 3"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine3"
-				},
-				{
-					"id": "province",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "province",
-					"label": {
-						"eng": "Province",
-						"sin": "පළාත",
-						"tam": "மாகாணம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": [
-						"province",
-						"district",
-						"divisionalSecretariat",
-						"grammaNiladhari"
-					],
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Province"
-				},
-				{
-					"id": "district",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "District",
-					"label": {
-						"eng": "District",
-						"sin": "දිස්ත්‍රික්කය",
-						"tam": "மாவட்டம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "District"
-				},
-				{
-					"id": "divisionalSecretariat",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Divisional Secretariat Division",
-					"label": {
-						"eng": "Divisional Secretariat Division",
-						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatDivision"
-				},
-				{
-					"id": "grammaNiladhari",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Grama Niladhari Division",
-					"label": {
-						"eng": "Grama Niladhari Division",
-						"sin": "ග්‍රාම නිලධාරී වසම",
-						"tam": "கிராம அலுவலர் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gramaNiladhariDivision"
-				},
-				{
-					"id": "postalCode",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "postalCode",
-					"label": {
-						"eng": "Postal Code",
-						"sin": "තැපැල් කේතය",
-						"tam": "அஞ்சல் குறியீடு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^[0-9]{5}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "postalCode"
-				},
-				{
-					"id": "currentAddressLine1",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine1",
-					"label": {
-						"eng": "Address Line 1",
-						"sin": "පළමු ලිපින පේළිය",
-						"tam": "முகவரி வரி 1"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine1"
-				},
-				{
-					"id": "currentAddressLine2",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine2",
-					"label": {
-						"eng": "Address Line 2",
-						"sin": "දෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 2"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine2"
-				},
-				{
-					"id": "currentAddressLine3",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine3",
-					"label": {
-						"eng": "Address Line 3",
-						"sin": "තෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 3"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine3"
-				},
-				{
-					"id": "currentProvince",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentProvince",
-					"label": {
-						"eng": "Province",
-						"sin": "පළාත",
-						"tam": "மாகாணம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": [
-						"currentProvince",
-						"currentDistrict",
-						"currentDivisionalSecretariat",
-						"currentGramaNiladhari"
-					],
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Province"
-				},
-				{
-					"id": "currentDistrict",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentDistrict",
-					"label": {
-						"eng": "District",
-						"sin": "දිස්ත්‍රික්කය",
-						"tam": "மாவட்டம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "District"
-				},
-				{
-					"id": "currentDivisionalSecretariat",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentDivisionalSecretariat",
-					"label": {
-						"eng": "Divisional Secretariat Division",
-						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatDivision"
-				},
-				{
-					"id": "currentGramaNiladhari",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentGramaNiladhari",
-					"label": {
-						"eng": "Grama Niladhari Division",
-						"sin": "ග්‍රාම නිලධාරී වසම",
-						"tam": "கிராம அலுவலர் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gramaNiladhariDivision"
-				},
-				{
-					"id": "currentPostalCode",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentPostalCode",
-					"label": {
-						"eng": "Current Postal Code",
-						"sin": "වර්තමාන තැපැල් කේතය",
-						"tam": "தற்போதைய அஞ்சல் குறியீடு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^$|^[0-9]{5}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentPostalCode"
-				},
-				{
-					"id": "referenceIdentityNumber",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "referenceIdentityNumber",
-					"label": {
-						"eng": "National ID Number",
-						"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
-						"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "kyc",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "ReferenceIdentityNumber",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "referenceIdentityNumber"
-				},
-				{
-					"id": "phone",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "phone",
-					"label": {
-						"eng": "Phone",
-						"sin": "දුරකථන අංකය",
-						"tam": "தொலைபேசி"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^7[0-9]{8}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Address",
-					"alignmentGroupLabel": {
-						"eng": "Address",
-						"sin": "ලිපිනය",
-						"tam": "முகவரி"
-					},
-					"visible": null,
-					"contactType": "email",
-					"group": "Phone",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Phone"
-				},
-				{
-					"id": "email",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
-	"id": "LOST",
-	"order": 3,
-	"flow": "LOST",
-	"isSubProcess": false,
-	"label": {
-		"eng": "Lost UIN",
-		"sin": "නැතිවූ SLUDI අංකය",
-		"tam": "இழந்த SLUDI எண்"
-	},
-	"screens": [
-		{
-			"order": 1,
-			"name": "consentdet",
-			"label": {
-				"eng": "Consent",
-				"sin": "එකඟතාව",
-				"tam": "இணக்கம்"
-			},
-			"caption": {
-				"eng": "Consent",
-				"sin": "එකඟතාව",
-				"tam": "இணக்கம்"
-			},
-			"fields": [
-				{
-					"id": "IDSchemaVersion",
-					"inputRequired": false,
-					"type": "number",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "ID Schema Version",
-					"label": {
-						"eng": "IDSchemaVersion",
-						"sin": "හැඳුනුම්පත් යෝජනා ක්‍රම අනුවාදය",
-						"tam": "அடையாளத் திட்டப் பதிப்பு"
-					},
-					"controlType": null,
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "none",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": null,
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "IdSchemaVersion"
-				},
-				{
-					"id": "consentText",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Consent",
-					"label": {},
-					"controlType": "html",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consentText",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": "Registration Consent",
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consentText"
-				},
-				{
-					"id": "consent",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "consent accepted",
-					"label": {
-						"eng": "I have read and accept terms and conditions to share my PII",
-						"sin": "මම මගේ පෞද්ගලික තොරතුරු බෙදා ගැනීමේ නියමයන් සහ කොන්දේසි කියවා එකඟ වෙමි",
-						"tam": "எனது தனிப்பட்ட தகவல்களைப் பகிர்வதற்கான நிபந்தனைகளைப் படித்து ஏற்றுக்கொள்கிறேன்"
-					},
-					"controlType": "checkbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consent",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consent"
-				},
-				{
-					"id": "preferredLang",
-					"inputRequired": false,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "user preferred Language",
-					"label": {
-						"eng": "Notification Language",
-						"sin": "දැනුම්දීමේ භාෂාව",
-						"tam": "அறிவிப்பு மொழி"
-					},
-					"controlType": "button",
-					"fieldType": "dynamic",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "group1",
-					"visible": null,
-					"contactType": null,
-					"group": "PreferredLanguage",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "preferredLang"
-				}
-			],
-			"layoutTemplate": null,
-			"preRegFetchRequired": false,
-			"active": false
-		},
-		{
-			"order": 2,
-			"name": "DemographicDetails",
-			"label": {
-				"eng": "Demographic Details",
-				"sin": "ජනවිකාස විස්තර",
-				"tam": "மக்கள்தொகை விவரங்கள்"
-			},
-			"caption": {
-				"eng": "Demographic Details",
-				"sin": "ජනවිකාස විස්තර",
-				"tam": "மக்கள்தொகை விவரங்கள்"
-			},
-			"fields": [
-				{
-					"id": "familyName",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Family Name",
-					"label": {
-						"eng": "Family Name",
-						"sin": "පෙළපත් නාමය",
-						"tam": "குடும்பப் பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{3,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "FamilyName",
-					"groupLabel": {
-						"eng": "Family Name",
-						"sin": "පෙළපත් නාමය",
-						"tam": "குடும்பப் பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "familyName"
-				},
-				{
-					"id": "name",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Name",
-					"label": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{3,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Name",
-					"groupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "name"
-				},
-				{
-					"id": "surname",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Surname",
-					"label": {
-						"eng": "Surname",
-						"sin": "වාසගම",
-						"tam": "குடும்பப்பெயர்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{3,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Name",
-					"alignmentGroupLabel": {
-						"eng": "Name",
-						"sin": "නම",
-						"tam": "பெயர்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Surname",
-					"groupLabel": {
-						"eng": "Surname",
-						"sin": "වාසගම",
-						"tam": "குடும்பப்பெயர்"
-					},
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "surname"
-				},
-				{
-					"id": "gender",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "gender",
-					"label": {
-						"eng": "Gender",
-						"sin": "ස්ත්‍රී පුරුෂ භාවය",
-						"tam": "பாலினம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "dynamic",
-					"format": "",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "Gender",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gender"
-				},
-				{
-					"id": "dateOfBirth",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "dateOfBirth",
-					"label": {
-						"eng": "DOB",
-						"sin": "උපන් දිනය",
-						"tam": "பிறந்த தேதி"
-					},
-					"controlType": "ageDate",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "DateOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "dateOfBirth"
-				},
-				{
-					"id": "placeOfBirth",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "placeOfBirth",
-					"label": {
-						"eng": "Place of Birth",
-						"sin": "උපන් ස්ථානය",
-						"tam": "பிறந்த இடம்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{2,128}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PlaceOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "placeOfBirth"
-				},
-				{
-					"id": "divisionalSecretariatOfBirth",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "divisionalSecretariatOfBirth",
-					"label": {
-						"eng": "Divisional Secretariat of Birth",
-						"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PlaceOfBirth",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatOfBirth"
-				},
-				{
-					"id": "addressLine1",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine1",
-					"label": {
-						"eng": "Address Line 1",
-						"sin": "පළමු ලිපින පේළිය",
-						"tam": "முகவரி வரி 1"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,128}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine1"
-				},
-				{
-					"id": "addressLine2",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine2",
-					"label": {
-						"eng": "Address Line 2",
-						"sin": "දෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 2"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine2"
-				},
-				{
-					"id": "addressLine3",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "addressLine3",
-					"label": {
-						"eng": "Address Line 3",
-						"sin": "තෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 3"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "addressLine3"
-				},
-				{
-					"id": "province",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "province",
-					"label": {
-						"eng": "Province",
-						"sin": "පළාත",
-						"tam": "மாகாணம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": [
-						"province",
-						"district",
-						"divisionalSecretariat",
-						"grammaNiladhari"
-					],
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Province"
-				},
-				{
-					"id": "district",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "District",
-					"label": {
-						"eng": "District",
-						"sin": "දිස්ත්‍රික්කය",
-						"tam": "மாவட்டம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "District"
-				},
-				{
-					"id": "divisionalSecretariat",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Divisional Secretariat Division",
-					"label": {
-						"eng": "Divisional Secretariat Division",
-						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatDivision"
-				},
-				{
-					"id": "grammaNiladhari",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Grama Niladhari Division",
-					"label": {
-						"eng": "Grama Niladhari Division",
-						"sin": "ග්‍රාම නිලධාරී වසම",
-						"tam": "கிராம அலுவலர் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?=.{1,50}$).*",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gramaNiladhariDivision"
-				},
-				{
-					"id": "postalCode",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "postalCode",
-					"label": {
-						"eng": "Postal Code",
-						"sin": "තැපැල් කේතය",
-						"tam": "அஞ்சல் குறியீடு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^[0-9]{5}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "PermanentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Permanent Address",
-						"sin": "ස්ථිර ලිපිනය",
-						"tam": "நிரந்தர முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "PermanentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "postalCode"
-				},
-				{
-					"id": "currentAddressLine1",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine1",
-					"label": {
-						"eng": "Address Line 1",
-						"sin": "පළමු ලිපින පේළිය",
-						"tam": "முகவரி வரி 1"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine1"
-				},
-				{
-					"id": "currentAddressLine2",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine2",
-					"label": {
-						"eng": "Address Line 2",
-						"sin": "දෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 2"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine2"
-				},
-				{
-					"id": "currentAddressLine3",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentAddressLine3",
-					"label": {
-						"eng": "Address Line 3",
-						"sin": "තෙවන ලිපින පේළිය",
-						"tam": "முகவரி வரி 3"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,128})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": true,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentAddressLine3"
-				},
-				{
-					"id": "currentProvince",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentProvince",
-					"label": {
-						"eng": "Province",
-						"sin": "පළාත",
-						"tam": "மாகாணம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": [
-						"currentProvince",
-						"currentDistrict",
-						"currentDivisionalSecretariat",
-						"currentGramaNiladhari"
-					],
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Province"
-				},
-				{
-					"id": "currentDistrict",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentDistrict",
-					"label": {
-						"eng": "District",
-						"sin": "දිස්ත්‍රික්කය",
-						"tam": "மாவட்டம்"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "District"
-				},
-				{
-					"id": "currentDivisionalSecretariat",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentDivisionalSecretariat",
-					"label": {
-						"eng": "Divisional Secretariat Division",
-						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-						"tam": "பிரதேச செயலகப் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "divisionalSecretariatDivision"
-				},
-				{
-					"id": "currentGramaNiladhari",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentGramaNiladhari",
-					"label": {
-						"eng": "Grama Niladhari Division",
-						"sin": "ග්‍රාම නිලධාරී වසම",
-						"tam": "கிராம அலுவலர் பிரிவு"
-					},
-					"controlType": "dropdown",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(|.{1,50})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "gramaNiladhariDivision"
-				},
-				{
-					"id": "currentPostalCode",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "currentPostalCode",
-					"label": {
-						"eng": "Current Postal Code",
-						"sin": "වර්තමාන තැපැල් කේතය",
-						"tam": "தற்போதைய அஞ்சல் குறியீடு"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^$|^[0-9]{5}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "CurrentAddress",
-					"alignmentGroupLabel": {
-						"eng": "Current Address",
-						"sin": "වර්තමාන ලිපිනය",
-						"tam": "தற்போதைய முகவரி"
-					},
-					"visible": null,
-					"contactType": "Postal",
-					"group": "CurrentAddress",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "currentPostalCode"
-				},
-				{
-					"id": "referenceIdentityNumber",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "referenceIdentityNumber",
-					"label": {
-						"eng": "National ID Number",
-						"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
-						"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "kyc",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Demographics",
-					"alignmentGroupLabel": {
-						"eng": "Demographics",
-						"sin": "ජන විකාශනය",
-						"tam": "மக்கள்தொகை விவரம்"
-					},
-					"visible": null,
-					"contactType": null,
-					"group": "ReferenceIdentityNumber",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "referenceIdentityNumber"
-				},
-				{
-					"id": "phone",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "phone",
-					"label": {
-						"eng": "Phone",
-						"sin": "දුරකථන අංකය",
-						"tam": "தொலைபேசி"
-					},
-					"controlType": "textbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [
-						{
-							"type": "regex",
-							"validator": "^7[0-9]{8}$",
-							"arguments": [],
-							"langCode": null
-						}
-					],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "Address",
-					"alignmentGroupLabel": {
-						"eng": "Address",
-						"sin": "ලිපිනය",
-						"tam": "முகவரி"
-					},
-					"visible": null,
-					"contactType": "email",
-					"group": "Phone",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "Phone"
-				},
-				{
-					"id": "email",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "email",
-				</t>
   </si>
   <si>
     <t>{
@@ -4382,6 +416,2652 @@
 	"isActive": true,
 	"autoSelectedGroups": null
 }</t>
+  </si>
+  <si>
+    <t>{"id":"NEW","order":1,"flow":"NEW","label":{"tam":"புதிய பதிவு","sin":"නව ලියාපදිංචිය","eng":"New Registration"},"screens":[{"order":1,"name":"consentdet","label":{"tam":"இணக்கம்","sin":"එකඟතාව","eng":"Consent"},"caption":{"tam":"இணக்கம்","sin":"එකඟතාව","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"tam":"அடையாளத் திட்டப் பதிப்பு","sin":"හැඳුනුම්පත් යෝජනා ක්‍රම අනුවාදය","eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"tam":"எனது தனிப்பட்ட தகவல்களைப் பகிர்வதற்கான நிபந்தனைகளைப் படித்து ஏற்றுக்கொள்கிறேன்","sin":"මම මගේ පෞද්ගලික තොරතුරු බෙදා ගැනීමේ නියමයන් සහ කොන්දේසි කියවා එකඟ වෙමි","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"tam":"அறிவிப்பு மொழி","sin":"දැනුම්දීමේ භාෂාව","eng":"Notification Language"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"tam":"மக்கள்தொகை விவரங்கள்","sin":"ජනවිකාස විස්තර","eng":"Demographic Details"},"caption":{"tam":"மக்கள்தொகை விவரங்கள்","sin":"ජනවිකාස විස්තර","eng":"Demographic Details"},"fields":[{"id":"familyName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Family Name","label":{"tam":"குடும்பப் பெயர்","sin":"පෙළපත් නාමය","eng":"Family Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{3,50})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Name","visible":null,"contactType":null,"group":"FamilyName","groupLabel":{"tam":"குடும்பப் பெயர்","sin":"පෙළපත් නාමය","eng":"Family Name"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"familyName","alignmentGroupLabel":{"eng":"Name","sin":"නම","tam":"பெயர்"}},{"id":"name","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Name","label":{"tam":"பெயர்","sin":"නම","eng":"Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Name","visible":null,"contactType":null,"group":"Name","groupLabel":{"tam":"பெயர்","sin":"නම","eng":"Name"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"name","alignmentGroupLabel":{"eng":"Name","sin":"නම","tam":"பெயர்"}},{"id":"surname","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Surname","label":{"tam":"குடும்பப்பெயர்","sin":"වාසගම","eng":"Surname"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Name","visible":null,"contactType":null,"group":"Surname","groupLabel":{"tam":"குடும்பப்பெயர்","sin":"වාසගම","eng":"Surname"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"surname","alignmentGroupLabel":{"eng":"Name","sin":"නම","tam":"பெயர்"}},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"tam":"பாலினம்","sin":"ස්ත්‍රී පුරුෂ භාවය","eng":"Gender"},"controlType":"dropdown","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"Demographics","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"gender","alignmentGroupLabel":{"eng":"Demographics","sin":"ජන විකාශනය","tam":"மக்கள்தொகை விவரம்"}},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"tam":"பிறந்த தேதி","sin":"උපන් දිනය","eng":"DOB"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Demographics","visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth","alignmentGroupLabel":{"eng":"Demographics","sin":"ජන විකාශනය","tam":"மக்கள்தொகை விவரம்"}},{"id":"placeOfBirth","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"placeOfBirth","label":{"tam":"பிறந்த இடம்","sin":"උපන් ස්ථානය","eng":"Place of Birth"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,128}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Demographics","visible":null,"contactType":null,"group":"PlaceOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"placeOfBirth","alignmentGroupLabel":{"eng":"Demographics","sin":"ජන විකාශනය","tam":"மக்கள்தொகை விவரம்"}},{"id":"divisionalSecretariatOfBirth","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"divisionalSecretariatOfBirth","label":{"tam":"பிறந்த பிரதேச செயலகப் பிரிவு","sin":"උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය","eng":"Divisional Secretariat of Birth"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{1,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Demographics","visible":null,"contactType":null,"group":"PlaceOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"divisionalSecretariatOfBirth","alignmentGroupLabel":{"eng":"Demographics","sin":"ජන විකාශනය","tam":"மக்கள்தொகை விவரம்"}},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"tam":"முகவரி வரி 1","sin":"පළමු ලිපින පේළිය","eng":"Address Line 1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{1,128}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":"Postal","group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"tam":"முகவரி வரி 2","sin":"දෙවන ලිපින පේළිය","eng":"Address Line 2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,128})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":"Postal","group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"addressLine3","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine3","label":{"tam":"முகவரி வரி 3","sin":"තෙවන ලිපින පේළිය","eng":"Address Line 3"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,128})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":"Postal","group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine3","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"province","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"province","label":{"tam":"மாகாணம்","sin":"පළාත","eng":"Province"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{1,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":"Postal","group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":["province","district","divisionalSecretariat","grammaNiladhari"],"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"Province","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"district","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"District","label":{"tam":"மாவட்டம்","sin":"දිස්ත්‍රික්කය","eng":"District"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{1,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":"Postal","group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"District","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"divisionalSecretariat","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Divisional Secretariat Division","label":{"tam":"பிரதேச செயலகப் பிரிவு","sin":"ප්‍රාදේශීය ලේකම් කොට්ඨාශය","eng":"Divisional Secretariat Division"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{1,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":"Postal","group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"divisionalSecretariatDivision","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"grammaNiladhari","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Grama Niladhari Division","label":{"tam":"கிராம அலுவலர் பிரிவு","sin":"ග්‍රාම නිලධාරී වසම","eng":"Grama Niladhari Division"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{1,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":null,"group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"gramaNiladhariDivision","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"postalCode","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"postalCode","label":{"tam":"அஞ்சல் குறியீடு","sin":"තැපැල් කේතය","eng":"Postal Code"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[0-9]{5}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"PermanentAddress","visible":null,"contactType":"Postal","group":"PermanentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"bioAttributes":null,"requiredOn":[],"subType":"postalCode","alignmentGroupLabel":{"eng":"Permanent Address","sin":"ස්ථිර ලිපිනය","tam":"நிரந்தர முகவரி"}},{"id":"currentAddressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"currentAddressLine1","label":{"tam":"முகவரி வரி 1","sin":"පළමු ලිපින පේළිය","eng":"Address Line 1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,128})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"currentAddressLine1","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"currentAddressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"currentAddressLine2","label":{"tam":"முகவரி வரி 2","sin":"දෙවන ලිපින පේළිය","eng":"Address Line 2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,128})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"currentAddressLine2","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"currentAddressLine3","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"currentAddressLine3","label":{"tam":"முகவரி வரி 3","sin":"තෙවන ලිපින පේළිය","eng":"Address Line 3"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,128})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"currentAddressLine3","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"currentProvince","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"currentProvince","label":{"tam":"மாகாணம்","sin":"පළාත","eng":"Province"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,50})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":["currentProvince","currentDistrict","currentDivisionalSecretariat","currentGramaNiladhari"],"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"Province","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"currentDistrict","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"currentDistrict","label":{"tam":"மாவட்டம்","sin":"දිස්ත්‍රික්කය","eng":"District"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,50})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"District","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"currentDivisionalSecretariat","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"currentDivisionalSecretariat","label":{"tam":"பிரதேச செயலகப் பிரிவு","sin":"ප්‍රාදේශීය ලේකම් කොට්ඨාශය","eng":"Divisional Secretariat Division"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,50})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"divisionalSecretariatDivision","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"currentGramaNiladhari","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"currentGramaNiladhari","label":{"tam":"கிராம அலுவலர் பிரிவு","sin":"ග්‍රාම නිලධාරී වසම","eng":"Grama Niladhari Division"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(|.{1,50})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"gramaNiladhariDivision","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"currentPostalCode","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"currentPostalCode","label":{"tam":"தற்போதைய அஞ்சல் குறியீடு","sin":"වර්තමාන තැපැල් කේතය","eng":"Current Postal Code"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^$|^[0-9]{5}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"CurrentAddress","visible":null,"contactType":"Postal","group":"CurrentAddress","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"currentPostalCode","alignmentGroupLabel":{"eng":"Current Address","sin":"වර්තමාන ලිපිනය","tam":"தற்போதைய முகவரி"}},{"id":"referenceIdentityNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"referenceIdentityNumber","label":{"tam":"தற்போதைய தேசிய அடையாள அட்டை எண்","sin":"පවතින ජාතික හැඳුනුම්පත් අංකය","eng":"National ID Number"},"controlType":"textbox","fieldType":"default","format":"kyc","validators":[{"type":"regex","validator":"^(?:\\d{9}[VXvx]|\\d{12})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Demographics","visible":null,"contactType":null,"group":"ReferenceIdentityNumber","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"referenceIdentityNumber","alignmentGroupLabel":{"eng":"Demographics","sin":"ජන විකාශනය","tam":"மக்கள்தொகை விவரம்"}},{"id":"phone","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"phone","label":{"tam":"தொலைபேசி","sin":"දුරකථන අංකය","eng":"Phone"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^7[0-9]{8}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Address","visible":null,"contactType":"email","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"Phone","alignmentGroupLabel":{"eng":"Address","sin":"ලිපිනය","tam":"முகவரி"}},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"tam":"மின்னஞ்சல்","sin":"විද්‍යුත් තැපෑල","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"Address","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"Email","alignmentGroupLabel":{"eng":"Address","sin":"ලිපිනය","tam":"முகவரி"}},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"tam":"அறிமுகப்படுத்துபவர் பெயர்","sin":"හඳුන්වා දෙන්නාගේ නම","eng":"Introducer Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"Introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName","alignmentGroupLabel":{"eng":"Introducer","sin":"හඳුන්වා දෙන්නා","tam":"அறிமுகப்படுத்துபவர்"}},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"tam":"அறிமுகப்படுத்துபவர் RID","sin":"හඳුන්වා දෙන්නාගේ RID","eng":"Introducer RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"Introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID","alignmentGroupLabel":{"eng":"Introducer","sin":"හඳුන්වා දෙන්නා","tam":"அறிமுகப்படுத்துபவர்"}},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"tam":"அறிமுகப்படுத்துபவர் SLUDI எண்","sin":"හඳුන්වා දෙන්නාගේ SLUDI අංකය","eng":"Introducer SLUDI"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"Introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN","alignmentGroupLabel":{"eng":"Introducer","sin":"හඳුන්වා දෙන්නා","tam":"அறிமுகப்படுத்துபவர்"}}],"layoutTemplate":null,"preRegFetchRequired":true,"active":false},{"order":3,"name":"Documents","label":{"tam":"ஆவணப் பதிவேற்றம்","sin":"ලේඛන උඩුගත කිරීම","eng":"Document Upload"},"caption":{"tam":"ஆவணங்கள்","sin":"ලේඛන","eng":"Documents"},"fields":[{"id":"proofOfAddress","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfAddress","label":{"tam":"முகவரி சான்று","sin":"පදිංචිය තහවුරු කිරීමේ සහතිකය","eng":"Address Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POA"},{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"tam":"அடையாளச் சான்று","sin":"අනන්‍යතා තහවුරු කිරීමේ සහතිකය","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":false,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"tam":"உறவுச் சான்று","sin":"සම්බන්ධතා සහතිකය","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":false,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"tam":"பிறந்த தேதிச் சான்று","sin":"උප්පැන්න සහතිකය","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POB"},{"id":"proofOfException","inputRequired":false,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"tam":"விதிவிலக்குச் சான்று","sin":"ව්‍යතිරේක සාධකය","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"tam":"உயிரியல்பதிவு விவரங்கள்","sin":"ජෛවමිතික විස්තර","eng":"Biometric Details"},"caption":{"tam":"உயிரியல்பதிவு விவரங்கள்","sin":"ජෛවමිතික විස්තර","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"tam":"விண்ணப்பதாரர் உயிரியல்பதிவு","sin":"අයදුම්කරුගේ ජෛවමිතික","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":5,"name":"IntroducerBiometricDetails","label":{"tam":"அறிமுகப்படுத்துபவர் உயிரியல்பதிவு விவரங்கள்","sin":"හඳුන්වා දෙන්නාගේ ජෛවමිතික විස්තර","eng":"Introducer Biometric Details"},"caption":{"tam":"அறிமுகப்படுத்துபவர் உயிரியல்பதிவு விவரங்கள்","sin":"හඳුන්වා දෙන්නාගේ ජෛවමිතික විස්තර","eng":"Introducer Biometric Details"},"fields":[{"id":"introducerBiometrics","inputRequired":true,"t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+	"id": "UPDATE",
+	"order": 2,
+	"flow": "UPDATE",
+	"label": {
+		"eng": "Update UIN",
+		"sin": "SLUDI අංකය යාවත්කාලීන කිරීම",
+		"tam": "SLUDI எண்ணைப் புதுப்பித்தல்"
+	},
+	"screens": [
+		{
+			"order": 1,
+			"name": "consentdet",
+			"label": {
+				"eng": "Consent",
+				"sin": "එකඟතාව",
+				"tam": "இணக்கம்"
+			},
+			"caption": {
+				"eng": "Consent",
+				"sin": "එකඟතාව",
+				"tam": "இணக்கம்"
+			},
+			"fields": [
+				{
+					"id": "IDSchemaVersion",
+					"inputRequired": false,
+					"type": "number",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "ID Schema Version",
+					"label": {
+						"eng": "IDSchemaVersion",
+						"sin": "හැඳුනුම්පත් යෝජනා ක්‍රම අනුවාදය",
+						"tam": "அடையாளத் திட்டப் பதிப்பு"
+					},
+					"controlType": null,
+					"fieldType": "default",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "none",
+					"alignmentGroup": null,
+					"visible": null,
+					"contactType": null,
+					"group": null,
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "IdSchemaVersion"
+				},
+				{
+					"id": "consentText",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Consent",
+					"label": {},
+					"controlType": "html",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "evidence",
+					"alignmentGroup": null,
+					"visible": null,
+					"contactType": null,
+					"group": "consentText",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": "Registration Consent",
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "consentText"
+				},
+				{
+					"id": "consent",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "consent accepted",
+					"label": {
+						"eng": "I have read and accept terms and conditions to share my PII",
+						"sin": "මම මගේ පෞද්ගලික තොරතුරු බෙදා ගැනීමේ නියමයන් සහ කොන්දේසි කියවා එකඟ වෙමි",
+						"tam": "எனது தனிப்பட்ட தகவல்களைப் பகிர்வதற்கான நிபந்தனைகளைப் படித்து ஏற்றுக்கொள்கிறேன்"
+					},
+					"controlType": "checkbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "evidence",
+					"alignmentGroup": null,
+					"visible": null,
+					"contactType": null,
+					"group": "consent",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "consent"
+				},
+				{
+					"id": "preferredLang",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "user preferred Language",
+					"label": {
+						"eng": "Notification Language",
+						"sin": "දැනුම්දීමේ භාෂාව",
+						"tam": "அறிவிப்பு மொழி"
+					},
+					"controlType": "button",
+					"fieldType": "dynamic",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "group1",
+					"visible": null,
+					"contactType": null,
+					"group": "PreferredLanguage",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "preferredLang"
+				}
+			],
+			"layoutTemplate": null,
+			"preRegFetchRequired": false,
+			"active": false
+		},
+		{
+			"order": 2,
+			"name": "DemographicDetails",
+			"label": {
+				"eng": "Demographic Details",
+				"sin": "ජනවිකාස විස්තර",
+				"tam": "மக்கள்தொகை விவரங்கள்"
+			},
+			"caption": {
+				"eng": "Demographic Details",
+				"sin": "ජනවිකාස විස්තර",
+				"tam": "மக்கள்தொகை விவரங்கள்"
+			},
+			"fields": [
+				{
+					"id": "familyName",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Family Name",
+					"label": {
+						"eng": "Family Name",
+						"sin": "පෙළපත් නාමය",
+						"tam": "குடும்பப் பெயர்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{3,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Name",
+					"visible": null,
+					"contactType": null,
+					"group": "FamilyName",
+					"groupLabel": {
+						"eng": "Family Name",
+						"sin": "පෙළපත් නාමය",
+						"tam": "குடும்பப் பெயர்"
+					},
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "familyName",
+					"alignmentGroupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					}
+				},
+				{
+					"id": "name",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Name",
+					"label": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{3,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Name",
+					"visible": null,
+					"contactType": null,
+					"group": "Name",
+					"groupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					},
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "name",
+					"alignmentGroupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					}
+				},
+				{
+					"id": "surname",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Surname",
+					"label": {
+						"eng": "Surname",
+						"sin": "වාසගම",
+						"tam": "குடும்பப்பெயர்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{3,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Name",
+					"visible": null,
+					"contactType": null,
+					"group": "Surname",
+					"groupLabel": {
+						"eng": "Surname",
+						"sin": "වාසගම",
+						"tam": "குடும்பப்பெயர்"
+					},
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "surname",
+					"alignmentGroupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					}
+				},
+				{
+					"id": "gender",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "gender",
+					"label": {
+						"eng": "Gender",
+						"sin": "ස්ත්‍රී පුරුෂ භාවය",
+						"tam": "பாலினம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "dynamic",
+					"format": "",
+					"validators": [],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "Gender",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "gender",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "dateOfBirth",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "dateOfBirth",
+					"label": {
+						"eng": "DOB",
+						"sin": "උපන් දිනය",
+						"tam": "பிறந்த தேதி"
+					},
+					"controlType": "ageDate",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "DateOfBirth",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "dateOfBirth",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "placeOfBirth",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "placeOfBirth",
+					"label": {
+						"eng": "Place of Birth",
+						"sin": "උපන් ස්ථානය",
+						"tam": "பிறந்த இடம்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{2,128}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "PlaceOfBirth",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "placeOfBirth",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "divisionalSecretariatOfBirth",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "divisionalSecretariatOfBirth",
+					"label": {
+						"eng": "Divisional Secretariat of Birth",
+						"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+						"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "PlaceOfBirth",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "divisionalSecretariatOfBirth",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "addressLine1",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "addressLine1",
+					"label": {
+						"eng": "Address Line 1",
+						"sin": "පළමු ලිපින පේළිය",
+						"tam": "முகவரி வரி 1"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,128}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "addressLine1",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "addressLine2",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "addressLine2",
+					"label": {
+						"eng": "Address Line 2",
+						"sin": "දෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 2"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "addressLine2",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "addressLine3",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "addressLine3",
+					"label": {
+						"eng": "Address Line 3",
+						"sin": "තෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 3"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "addressLine3",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "province",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "province",
+					"label": {
+						"eng": "Province",
+						"sin": "පළාත",
+						"tam": "மாகாணம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": [
+						"province",
+						"district",
+						"divisionalSecretariat",
+						"grammaNiladhari"
+					],
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "Province",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "district",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "District",
+					"label": {
+						"eng": "District",
+						"sin": "දිස්ත්‍රික්කය",
+						"tam": "மாவட்டம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "District",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "divisionalSecretariat",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Divisional Secretariat Division",
+					"label": {
+						"eng": "Divisional Secretariat Division",
+						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+						"tam": "பிரதேச செயலகப் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "divisionalSecretariatDivision",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "grammaNiladhari",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Grama Niladhari Division",
+					"label": {
+						"eng": "Grama Niladhari Division",
+						"sin": "ග්‍රාම නිලධාරී වසම",
+						"tam": "கிராம அலுவலர் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": null,
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "gramaNiladhariDivision",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "postalCode",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "postalCode",
+					"label": {
+						"eng": "Postal Code",
+						"sin": "තැපැල් කේතය",
+						"tam": "அஞ்சல் குறியீடு"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^[0-9]{5}$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "postalCode",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "currentAddressLine1",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentAddressLine1",
+					"label": {
+						"eng": "Address Line 1",
+						"sin": "පළමු ලිපින පේළිය",
+						"tam": "முகவரி வரி 1"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentAddressLine1",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentAddressLine2",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentAddressLine2",
+					"label": {
+						"eng": "Address Line 2",
+						"sin": "දෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 2"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentAddressLine2",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentAddressLine3",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentAddressLine3",
+					"label": {
+						"eng": "Address Line 3",
+						"sin": "තෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 3"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentAddressLine3",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentProvince",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentProvince",
+					"label": {
+						"eng": "Province",
+						"sin": "පළාත",
+						"tam": "மாகாணம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": [
+						"currentProvince",
+						"currentDistrict",
+						"currentDivisionalSecretariat",
+						"currentGramaNiladhari"
+					],
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "Province",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentDistrict",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentDistrict",
+					"label": {
+						"eng": "District",
+						"sin": "දිස්ත්‍රික්කය",
+						"tam": "மாவட்டம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "District",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentDivisionalSecretariat",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentDivisionalSecretariat",
+					"label": {
+						"eng": "Divisional Secretariat Division",
+						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+						"tam": "பிரதேச செயலகப் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "divisionalSecretariatDivision",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentGramaNiladhari",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentGramaNiladhari",
+					"label": {
+						"eng": "Grama Niladhari Division",
+						"sin": "ග්‍රාම නිලධාරී වසම",
+						"tam": "கிராம அலுவலர் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "gramaNiladhariDivision",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentPostalCode",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentPostalCode",
+					"label": {
+						"eng": "Current Postal Code",
+						"sin": "වර්තමාන තැපැල් කේතය",
+						"tam": "தற்போதைய அஞ்சல் குறியீடு"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^$|^[0-9]{5}$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentPostalCode",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "referenceIdentityNumber",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "referenceIdentityNumber",
+					"label": {
+						"eng": "National ID Number",
+						"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
+						"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "kyc",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "ReferenceIdentityNumber",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "referenceIdentityNumber",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "phone",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "phone",
+					"label": {
+						"eng": "Phone",
+						"sin": "දුරකථන අංකය",
+						"tam": "தொலைபேசி"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^7[0-9]{8}$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Address",
+					"visible": null,
+					"contactType": "email",
+					"group": "Phone",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "Phone",
+					"alignmentGroupLabel": {
+						"eng": "Address",
+						"sin": "ලිපිනය",
+						"tam": "முகவரி"
+					}
+				},
+				{
+					"id": "email",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "email",
+					"label": </t>
+  </si>
+  <si>
+    <t>{
+	"id": "LOST",
+	"order": 3,
+	"flow": "LOST",
+	"label": {
+		"eng": "Lost UIN",
+		"sin": "නැතිවූ SLUDI අංකය",
+		"tam": "இழந்த SLUDI எண்"
+	},
+	"screens": [
+		{
+			"order": 1,
+			"name": "consentdet",
+			"label": {
+				"eng": "Consent",
+				"sin": "එකඟතාව",
+				"tam": "இணக்கம்"
+			},
+			"caption": {
+				"eng": "Consent",
+				"sin": "එකඟතාව",
+				"tam": "இணக்கம்"
+			},
+			"fields": [
+				{
+					"id": "IDSchemaVersion",
+					"inputRequired": false,
+					"type": "number",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "ID Schema Version",
+					"label": {
+						"eng": "IDSchemaVersion",
+						"sin": "හැඳුනුම්පත් යෝජනා ක්‍රම අනුවාදය",
+						"tam": "அடையாளத் திட்டப் பதிப்பு"
+					},
+					"controlType": null,
+					"fieldType": "default",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "none",
+					"alignmentGroup": null,
+					"visible": null,
+					"contactType": null,
+					"group": null,
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "IdSchemaVersion"
+				},
+				{
+					"id": "consentText",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Consent",
+					"label": {},
+					"controlType": "html",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "evidence",
+					"alignmentGroup": null,
+					"visible": null,
+					"contactType": null,
+					"group": "consentText",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": "Registration Consent",
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "consentText"
+				},
+				{
+					"id": "consent",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "consent accepted",
+					"label": {
+						"eng": "I have read and accept terms and conditions to share my PII",
+						"sin": "මම මගේ පෞද්ගලික තොරතුරු බෙදා ගැනීමේ නියමයන් සහ කොන්දේසි කියවා එකඟ වෙමි",
+						"tam": "எனது தனிப்பட்ட தகவல்களைப் பகிர்வதற்கான நிபந்தனைகளைப் படித்து ஏற்றுக்கொள்கிறேன்"
+					},
+					"controlType": "checkbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "evidence",
+					"alignmentGroup": null,
+					"visible": null,
+					"contactType": null,
+					"group": "consent",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "consent"
+				},
+				{
+					"id": "preferredLang",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "user preferred Language",
+					"label": {
+						"eng": "Notification Language",
+						"sin": "දැනුම්දීමේ භාෂාව",
+						"tam": "அறிவிப்பு மொழி"
+					},
+					"controlType": "button",
+					"fieldType": "dynamic",
+					"format": "none",
+					"validators": [],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "group1",
+					"visible": null,
+					"contactType": null,
+					"group": "PreferredLanguage",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": true,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "preferredLang"
+				}
+			],
+			"layoutTemplate": null,
+			"preRegFetchRequired": false,
+			"active": false
+		},
+		{
+			"order": 2,
+			"name": "DemographicDetails",
+			"label": {
+				"eng": "Demographic Details",
+				"sin": "ජනවිකාස විස්තර",
+				"tam": "மக்கள்தொகை விவரங்கள்"
+			},
+			"caption": {
+				"eng": "Demographic Details",
+				"sin": "ජනවිකාස විස්තර",
+				"tam": "மக்கள்தொகை விவரங்கள்"
+			},
+			"fields": [
+				{
+					"id": "familyName",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Family Name",
+					"label": {
+						"eng": "Family Name",
+						"sin": "පෙළපත් නාමය",
+						"tam": "குடும்பப் பெயர்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{3,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Name",
+					"visible": null,
+					"contactType": null,
+					"group": "FamilyName",
+					"groupLabel": {
+						"eng": "Family Name",
+						"sin": "පෙළපත් නාමය",
+						"tam": "குடும்பப் பெயர்"
+					},
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "familyName",
+					"alignmentGroupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					}
+				},
+				{
+					"id": "name",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Name",
+					"label": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{3,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Name",
+					"visible": null,
+					"contactType": null,
+					"group": "Name",
+					"groupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					},
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "name",
+					"alignmentGroupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					}
+				},
+				{
+					"id": "surname",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Surname",
+					"label": {
+						"eng": "Surname",
+						"sin": "වාසගම",
+						"tam": "குடும்பப்பெயர்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{3,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Name",
+					"visible": null,
+					"contactType": null,
+					"group": "Surname",
+					"groupLabel": {
+						"eng": "Surname",
+						"sin": "වාසගම",
+						"tam": "குடும்பப்பெயர்"
+					},
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "surname",
+					"alignmentGroupLabel": {
+						"eng": "Name",
+						"sin": "නම",
+						"tam": "பெயர்"
+					}
+				},
+				{
+					"id": "gender",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "gender",
+					"label": {
+						"eng": "Gender",
+						"sin": "ස්ත්‍රී පුරුෂ භාවය",
+						"tam": "பாலினம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "dynamic",
+					"format": "",
+					"validators": [],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "Gender",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "gender",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "dateOfBirth",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "dateOfBirth",
+					"label": {
+						"eng": "DOB",
+						"sin": "උපන් දිනය",
+						"tam": "பிறந்த தேதி"
+					},
+					"controlType": "ageDate",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "DateOfBirth",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "dateOfBirth",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "placeOfBirth",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "placeOfBirth",
+					"label": {
+						"eng": "Place of Birth",
+						"sin": "උපන් ස්ථානය",
+						"tam": "பிறந்த இடம்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{2,128}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "PlaceOfBirth",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "placeOfBirth",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "divisionalSecretariatOfBirth",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "divisionalSecretariatOfBirth",
+					"label": {
+						"eng": "Divisional Secretariat of Birth",
+						"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+						"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "PlaceOfBirth",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "divisionalSecretariatOfBirth",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "addressLine1",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "addressLine1",
+					"label": {
+						"eng": "Address Line 1",
+						"sin": "පළමු ලිපින පේළිය",
+						"tam": "முகவரி வரி 1"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,128}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "addressLine1",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "addressLine2",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "addressLine2",
+					"label": {
+						"eng": "Address Line 2",
+						"sin": "දෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 2"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "addressLine2",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "addressLine3",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "addressLine3",
+					"label": {
+						"eng": "Address Line 3",
+						"sin": "තෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 3"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "addressLine3",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "province",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "province",
+					"label": {
+						"eng": "Province",
+						"sin": "පළාත",
+						"tam": "மாகாணம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": [
+						"province",
+						"district",
+						"divisionalSecretariat",
+						"grammaNiladhari"
+					],
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "Province",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "district",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "District",
+					"label": {
+						"eng": "District",
+						"sin": "දිස්ත්‍රික්කය",
+						"tam": "மாவட்டம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "District",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "divisionalSecretariat",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Divisional Secretariat Division",
+					"label": {
+						"eng": "Divisional Secretariat Division",
+						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+						"tam": "பிரதேச செயலகப் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "divisionalSecretariatDivision",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "grammaNiladhari",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "Grama Niladhari Division",
+					"label": {
+						"eng": "Grama Niladhari Division",
+						"sin": "ග්‍රාම නිලධාරී වසම",
+						"tam": "கிராம அலுவலர் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?=.{1,50}$).*",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": null,
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "gramaNiladhariDivision",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "postalCode",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "postalCode",
+					"label": {
+						"eng": "Postal Code",
+						"sin": "තැපැල් කේතය",
+						"tam": "அஞ்சல் குறியீடு"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^[0-9]{5}$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "PermanentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "PermanentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "postalCode",
+					"alignmentGroupLabel": {
+						"eng": "Permanent Address",
+						"sin": "ස්ථිර ලිපිනය",
+						"tam": "நிரந்தர முகவரி"
+					}
+				},
+				{
+					"id": "currentAddressLine1",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentAddressLine1",
+					"label": {
+						"eng": "Address Line 1",
+						"sin": "පළමු ලිපින පේළිය",
+						"tam": "முகவரி வரி 1"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentAddressLine1",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentAddressLine2",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentAddressLine2",
+					"label": {
+						"eng": "Address Line 2",
+						"sin": "දෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 2"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentAddressLine2",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentAddressLine3",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentAddressLine3",
+					"label": {
+						"eng": "Address Line 3",
+						"sin": "තෙවන ලිපින පේළිය",
+						"tam": "முகவரி வரி 3"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,128})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": true,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentAddressLine3",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentProvince",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentProvince",
+					"label": {
+						"eng": "Province",
+						"sin": "පළාත",
+						"tam": "மாகாணம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": [
+						"currentProvince",
+						"currentDistrict",
+						"currentDivisionalSecretariat",
+						"currentGramaNiladhari"
+					],
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "Province",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentDistrict",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentDistrict",
+					"label": {
+						"eng": "District",
+						"sin": "දිස්ත්‍රික්කය",
+						"tam": "மாவட்டம்"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "District",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentDivisionalSecretariat",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentDivisionalSecretariat",
+					"label": {
+						"eng": "Divisional Secretariat Division",
+						"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+						"tam": "பிரதேச செயலகப் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "divisionalSecretariatDivision",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentGramaNiladhari",
+					"inputRequired": true,
+					"type": "simpleType",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentGramaNiladhari",
+					"label": {
+						"eng": "Grama Niladhari Division",
+						"sin": "ග්‍රාම නිලධාරී වසම",
+						"tam": "கிராம அலுவலர் பிரிவு"
+					},
+					"controlType": "dropdown",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(|.{1,50})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "gramaNiladhariDivision",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "currentPostalCode",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "currentPostalCode",
+					"label": {
+						"eng": "Current Postal Code",
+						"sin": "වර්තමාන තැපැල් කේතය",
+						"tam": "தற்போதைய அஞ்சல் குறியீடு"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^$|^[0-9]{5}$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "CurrentAddress",
+					"visible": null,
+					"contactType": "Postal",
+					"group": "CurrentAddress",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "currentPostalCode",
+					"alignmentGroupLabel": {
+						"eng": "Current Address",
+						"sin": "වර්තමාන ලිපිනය",
+						"tam": "தற்போதைய முகவரி"
+					}
+				},
+				{
+					"id": "referenceIdentityNumber",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "referenceIdentityNumber",
+					"label": {
+						"eng": "National ID Number",
+						"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
+						"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "kyc",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Demographics",
+					"visible": null,
+					"contactType": null,
+					"group": "ReferenceIdentityNumber",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "referenceIdentityNumber",
+					"alignmentGroupLabel": {
+						"eng": "Demographics",
+						"sin": "ජන විකාශනය",
+						"tam": "மக்கள்தொகை விவரம்"
+					}
+				},
+				{
+					"id": "phone",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "phone",
+					"label": {
+						"eng": "Phone",
+						"sin": "දුරකථන අංකය",
+						"tam": "தொலைபேசி"
+					},
+					"controlType": "textbox",
+					"fieldType": "default",
+					"format": "none",
+					"validators": [
+						{
+							"type": "regex",
+							"validator": "^7[0-9]{8}$",
+							"arguments": [],
+							"langCode": null
+						}
+					],
+					"fieldCategory": "pvt",
+					"alignmentGroup": "Address",
+					"visible": null,
+					"contactType": "email",
+					"group": "Phone",
+					"groupLabel": null,
+					"changeAction": null,
+					"transliterate": false,
+					"templateName": null,
+					"fieldLayout": null,
+					"locationHierarchy": null,
+					"conditionalBioAttributes": null,
+					"required": false,
+					"bioAttributes": null,
+					"requiredOn": [],
+					"subType": "Phone",
+					"alignmentGroupLabel": {
+						"eng": "Address",
+						"sin": "ලිපිනය",
+						"tam": "முகவரி"
+					}
+				},
+				{
+					"id": "email",
+					"inputRequired": true,
+					"type": "string",
+					"minimum": 0,
+					"maximum": 0,
+					"description": "email",
+					"label": {
+						"eng": "</t>
   </si>
   <si>
     <t>{
@@ -4766,12 +3446,30 @@
 				"alignmentGroup": "Permanent Address"
 			},
 			{
+				"id": "sameAsPermanentAddress",
+				"description": "Same as Permanent Address Checkbox",
+				"labelName": {
+					"eng": "Same as Permanent Address",
+					"sin": "ස්ථිර ලිපිනයට සමානයි",
+					"tam": "நிரந்தர முகவரிக்கு ஒத்ததாக"
+				},
+				"controlType": "checkbox",
+				"inputRequired": true,
+				"fieldType": "default",
+				"type": "boolean",
+				"validators": [],
+				"required": false,
+				"transliteration": false,
+				"alignmentGroup": "Current Address",
+				"changeAction": "copy&amp;disable:addressLine1=currentAddressLine1,addressLine2=currentAddressLine2,addressLine3=currentAddressLine3,province=currentProvince,district=currentDistrict,divisionalSecretariat=currentDivisionalSecretariat,grammaNiladhari=currentGramaNiladhari,postalCode=currentPostalCode"
+			},
+			{
 				"id": "currentAddressLine1",
 				"description": "currentAddressLine1",
 				"labelName": {
-					"eng": "Address Line 1",
-					"sin": "පළමු ලිපින පේළිය",
-					"tam": "முகவரி வரி 1"
+					"eng": "Current Address Line 1",
+					"sin": "වත්මන් පළමු ලිපින පේළිය",
+					"tam": "தற்போதைய முகவரி வரி 1"
 				},
 				"controlType": "textbox",
 				"inputRequired": true,
@@ -4792,9 +3490,9 @@
 				"id": "currentAddressLine2",
 				"description": "currentAddressLine2",
 				"labelName": {
-					"eng": "Address Line 2",
-					"sin": "දෙවන ලිපින පේළිය",
-					"tam": "முகவரி வரி 2"
+					"eng": "Current Address Line 2",
+					"sin": "වත්මන් දෙවන ලිපින පේළිය",
+					"tam": "தற்போதைய முகவரி வரி 2"
 				},
 				"controlType": "textbox",
 				"inputRequired": true,
@@ -4815,9 +3513,9 @@
 				"id": "currentAddressLine3",
 				"description": "currentAddressLine3",
 				"labelName": {
-					"eng": "Address Line 3",
-					"sin": "තෙවන ලිපින පේළිය",
-					"tam": "முகவரி வரி 3"
+					"eng": "Current Address Line 3",
+					"sin": "වත්මන් තෙවන ලිපින පේළිය",
+					"tam": "தற்போதைய முகவரி வரி 3"
 				},
 				"controlType": "textbox",
 				"inputRequired": true,
@@ -4838,9 +3536,9 @@
 				"id": "currentProvince",
 				"description": "currentProvince",
 				"labelName": {
-					"eng": "Province",
-					"sin": "පළාත",
-					"tam": "மாகாணம்"
+					"eng": "Current Province",
+					"sin": "වත්මන් පළාත",
+					"tam": "තற்பෝதைய மாகாணம்"
 				},
 				"controlType": "dropdown",
 				"inputRequired": true,
@@ -4863,9 +3561,9 @@
 				"id": "currentDistrict",
 				"description": "currentDistrict",
 				"labelName": {
-					"eng": "District",
-					"sin": "දිස්ත්‍රික්කය",
-					"tam": "மாவட்டம்"
+					"eng": "Current District",
+					"sin": "වත්මන් දිස්ත්‍රික්කය",
+					"tam": "තற்பෝதைய மாவட்டம்"
 				},
 				"controlType": "dropdown",
 				"inputRequired": true,
@@ -4887,9 +3585,9 @@
 				"id": "currentDivisionalSecretariat",
 				"description": "currentDivisionalSecretariat",
 				"labelName": {
-					"eng": "Divisional Secretariat Division",
-					"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-					"tam": "பிரதேச செயலகப் பிரிவு"
+					"eng": "Current Divisional Secretariat Division",
+					"sin": "වත්මන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
+					"tam": "தற்போதைய பிரதேச செயலகப் பிரிவு"
 				},
 				"controlType": "dropdown",
 				"inputRequired": true,
@@ -4911,9 +3609,9 @@
 				"id": "currentGramaNiladhari",
 				"description": "currentGramaNiladhari",
 				"labelName": {
-					"eng": "Grama Niladhari Division",
-					"sin": "ග්‍රාම නිලධාරී වසම",
-					"tam": "கிராம அலுவலர் பிரிவு"
+					"eng": "Current Grama Niladhari Division",
+					"sin": "වත්මන් ග්‍රාම නිලධාරී වසම",
+					"tam": "தற்போதைய கிராம அலுவலர் பிரிவு"
 				},
 				"controlType": "dropdown",
 				"inputRequired": true,
@@ -4936,8 +3634,8 @@
 				"description": "currentPostalCode",
 				"labelName": {
 					"eng": "Current Postal Code",
-					"sin": "වර්තමාන තැපැල් කේතය",
-					"tam": "தற்போதைய அஞ்சல் குறியீடு"
+					"sin": "වත්මන් තැපැල් කේතය",
+					"tam": "තற்பෝதைய அஞ்சல் குறியீடு"
 				},
 				"controlType": "textbox",
 				"inputRequired": true,
@@ -4946,7 +3644,7 @@
 				"validators": [
 					{
 						"type": "regex",
-						"validator": "^$|^[0-9]{5}$",
+						"validator": "^[0-9]{5}$",
 						"arguments": []
 					}
 				],
@@ -5583,7 +4281,7 @@
         <v>36</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="2">
         <v>1001</v>
@@ -5645,7 +4343,7 @@
         <v>39</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="2">
         <v>1001</v>
@@ -5707,7 +4405,7 @@
         <v>42</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="2">
         <v>1001</v>
@@ -5769,7 +4467,7 @@
         <v>45</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2">
         <v>1001</v>

--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\mosip-training\sludi-mvp-dev-mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017A40AF-3E26-46B8-89CF-C4707889C7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41071D4C-5F25-4F66-8CE3-313B14C5CCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2784" yWindow="3228" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3064,710 +3064,710 @@
 						"eng": "</t>
   </si>
   <si>
-    <t>{
-	"identity": {
-		"identity": [
-			{
-				"id": "IDSchemaVersion",
-				"description": "ID Schema Version",
-				"type": "number",
-				"controlType": null,
-				"fieldType": "default",
-				"inputRequired": false,
-				"validators": [],
-				"required": true
-			},
-			{
-				"id": "familyName",
-				"description": "Family Name",
-				"labelName": {
-					"eng": "Family Name",
-					"sin": "පෙළපත් නාමය",
-					"tam": "குடும்பப் பெயர்"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{3,50})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": true,
-				"alignmentGroup": "Name"
-			},
-			{
-				"id": "name",
-				"description": "Name",
-				"labelName": {
-					"eng": "Name",
-					"sin": "නම",
-					"tam": "பெயர்"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{3,50}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": true,
-				"alignmentGroup": "Name"
-			},
-			{
-				"id": "surname",
-				"description": "Surname",
-				"labelName": {
-					"eng": "Surname",
-					"sin": "වාසගම",
-					"tam": "குடும்பப்பெயர்"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{3,50}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": true,
-				"alignmentGroup": "Name"
-			},
-			{
-				"id": "gender",
-				"description": "gender",
-				"labelName": {
-					"eng": "Gender",
-					"sin": "ස්ත්‍රී පුරුෂ භාවය",
-					"tam": "பாலினம்"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "dynamic",
-				"type": "simpleType",
-				"validators": [],
-				"required": true,
-				"transliteration": false,
-				"subType": "gender",
-				"alignmentGroup": "Demographics"
-			},
-			{
-				"id": "dateOfBirth",
-				"description": "dateOfBirth",
-				"labelName": {
-					"eng": "Date of Birth",
-					"sin": "උපන් දිනය",
-					"tam": "பிறந்த தேதி"
-				},
-				"controlType": "ageDate",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "string",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": false,
-				"alignmentGroup": "Demographics"
-			},
-			{
-				"id": "placeOfBirth",
-				"description": "placeOfBirth",
-				"labelName": {
-					"eng": "Place of Birth",
-					"sin": "උපන් ස්ථානය",
-					"tam": "பிறந்த இடம்"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{2,128}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": true,
-				"alignmentGroup": "Demographics"
-			},
-			{
-				"id": "divisionalSecretariatOfBirth",
-				"description": "divisionalSecretariatOfBirth",
-				"labelName": {
-					"eng": "Divisional Secretariat of Birth",
-					"sin": "උපන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-					"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{1,50}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": true,
-				"alignmentGroup": "Demographics"
-			},
-			{
-				"id": "referenceIdentityNumber",
-				"description": "referenceIdentityNumber",
-				"labelName": {
-					"eng": "Existing National ID Number",
-					"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",
-					"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "string",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Identifiers"
-			},
-			{
-				"id": "addressLine1",
-				"description": "addressLine1",
-				"labelName": {
-					"eng": "Address Line 1",
-					"sin": "පළමු ලිපින පේළිය",
-					"tam": "முகவரி வரி 1"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{1,128}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": true,
-				"alignmentGroup": "Permanent Address"
-			},
-			{
-				"id": "addressLine2",
-				"description": "addressLine2",
-				"labelName": {
-					"eng": "Address Line 2",
-					"sin": "දෙවන ලිපින පේළිය",
-					"tam": "முகவரி வரி 2"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,128})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": true,
-				"alignmentGroup": "Permanent Address"
-			},
-			{
-				"id": "addressLine3",
-				"description": "addressLine3",
-				"labelName": {
-					"eng": "Address Line 3",
-					"sin": "තෙවන ලිපින පේළිය",
-					"tam": "முகவரி வரி 3"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,128})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": true,
-				"alignmentGroup": "Permanent Address"
-			},
-			{
-				"id": "province",
-				"description": "province",
-				"labelName": {
-					"eng": "Province",
-					"sin": "පළාත",
-					"tam": "மாகாணம்"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{1,50}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": false,
-				"alignmentGroup": "Permanent Address",
-				"locationHierarchyLevel": 1,
-				"parentLocCode": "LKA"
-			},
-			{
-				"id": "district",
-				"description": "district",
-				"labelName": {
-					"eng": "District",
-					"sin": "දිස්ත්‍රික්කය",
-					"tam": "மாவட்டம்"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{1,50}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": false,
-				"alignmentGroup": "Permanent Address",
-				"locationHierarchyLevel": 2
-			},
-			{
-				"id": "divisionalSecretariat",
-				"description": "divisionalSecretariat",
-				"labelName": {
-					"eng": "Divisional Secretariat Division",
-					"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-					"tam": "பிரதேச செயலகப் பிரிவு"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{1,50}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": false,
-				"alignmentGroup": "Permanent Address",
-				"locationHierarchyLevel": 3
-			},
-			{
-				"id": "grammaNiladhari",
-				"description": "grammaNiladhari",
-				"labelName": {
-					"eng": "Grama Niladhari Division",
-					"sin": "ග්‍රාම නිලධාරී වසම",
-					"tam": "கிராம அலுவலர் பிரிவு"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(?=.{1,50}$).*",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": false,
-				"alignmentGroup": "Permanent Address",
-				"locationHierarchyLevel": 4
-			},
-			{
-				"id": "postalCode",
-				"description": "postalCode",
-				"labelName": {
-					"eng": "Postal Code",
-					"sin": "තැපැල් කේතය",
-					"tam": "அஞ்சல் குறியீடு"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "string",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^[0-9]{5}$",
-						"arguments": []
-					}
-				],
-				"required": true,
-				"transliteration": false,
-				"alignmentGroup": "Permanent Address"
-			},
-			{
-				"id": "sameAsPermanentAddress",
-				"description": "Same as Permanent Address Checkbox",
-				"labelName": {
-					"eng": "Same as Permanent Address",
-					"sin": "ස්ථිර ලිපිනයට සමානයි",
-					"tam": "நிரந்தர முகவரிக்கு ஒத்ததாக"
-				},
-				"controlType": "checkbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "boolean",
-				"validators": [],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Current Address",
-				"changeAction": "copy&amp;disable:addressLine1=currentAddressLine1,addressLine2=currentAddressLine2,addressLine3=currentAddressLine3,province=currentProvince,district=currentDistrict,divisionalSecretariat=currentDivisionalSecretariat,grammaNiladhari=currentGramaNiladhari,postalCode=currentPostalCode"
-			},
-			{
-				"id": "currentAddressLine1",
-				"description": "currentAddressLine1",
-				"labelName": {
-					"eng": "Current Address Line 1",
-					"sin": "වත්මන් පළමු ලිපින පේළිය",
-					"tam": "தற்போதைய முகவரி வரி 1"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,128})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": true,
-				"alignmentGroup": "Current Address"
-			},
-			{
-				"id": "currentAddressLine2",
-				"description": "currentAddressLine2",
-				"labelName": {
-					"eng": "Current Address Line 2",
-					"sin": "වත්මන් දෙවන ලිපින පේළිය",
-					"tam": "தற்போதைய முகவரி வரி 2"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,128})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": true,
-				"alignmentGroup": "Current Address"
-			},
-			{
-				"id": "currentAddressLine3",
-				"description": "currentAddressLine3",
-				"labelName": {
-					"eng": "Current Address Line 3",
-					"sin": "වත්මන් තෙවන ලිපින පේළිය",
-					"tam": "தற்போதைய முகவரி வரி 3"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,128})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": true,
-				"alignmentGroup": "Current Address"
-			},
-			{
-				"id": "currentProvince",
-				"description": "currentProvince",
-				"labelName": {
-					"eng": "Current Province",
-					"sin": "වත්මන් පළාත",
-					"tam": "තற்பෝதைய மாகாணம்"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,50})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Current Address",
-				"locationHierarchyLevel": 1,
-				"parentLocCode": "LKA"
-			},
-			{
-				"id": "currentDistrict",
-				"description": "currentDistrict",
-				"labelName": {
-					"eng": "Current District",
-					"sin": "වත්මන් දිස්ත්‍රික්කය",
-					"tam": "තற்பෝதைய மாவட்டம்"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,50})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Current Address",
-				"locationHierarchyLevel": 2
-			},
-			{
-				"id": "currentDivisionalSecretariat",
-				"description": "currentDivisionalSecretariat",
-				"labelName": {
-					"eng": "Current Divisional Secretariat Division",
-					"sin": "වත්මන් ප්‍රාදේශීය ලේකම් කොට්ඨාශය",
-					"tam": "தற்போதைய பிரதேச செயலகப் பிரிவு"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,50})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Current Address",
-				"locationHierarchyLevel": 3
-			},
-			{
-				"id": "currentGramaNiladhari",
-				"description": "currentGramaNiladhari",
-				"labelName": {
-					"eng": "Current Grama Niladhari Division",
-					"sin": "වත්මන් ග්‍රාම නිලධාරී වසම",
-					"tam": "தற்போதைய கிராம அலுவலர் பிரிவு"
-				},
-				"controlType": "dropdown",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "simpleType",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(|.{1,50})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Current Address",
-				"locationHierarchyLevel": 4
-			},
-			{
-				"id": "currentPostalCode",
-				"description": "currentPostalCode",
-				"labelName": {
-					"eng": "Current Postal Code",
-					"sin": "වත්මන් තැපැල් කේතය",
-					"tam": "තற்பෝதைய அஞ்சல் குறியீடு"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "string",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^[0-9]{5}$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Current Address"
-			},
-			{
-				"id": "phone",
-				"description": "phone",
-				"labelName": {
-					"eng": "Phone",
-					"sin": "දුරකථන අංකය",
-					"tam": "தொலைபேசி"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "string",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^(0?7[0-9]{8})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Contact"
-			},
-			{
-				"id": "email",
-				"description": "email",
-				"labelName": {
-					"eng": "Email",
-					"sin": "විද්‍යුත් තැපෑල",
-					"tam": "மின்னஞ்சல்"
-				},
-				"controlType": "textbox",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "string",
-				"validators": [
-					{
-						"type": "regex",
-						"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
-						"arguments": []
-					}
-				],
-				"required": false,
-				"transliteration": false,
-				"alignmentGroup": "Contact"
-			},
-			{
-				"id": "proofOfAddress",
-				"description": "proofOfAddress",
-				"labelName": {
-					"eng": "Address Proof",
-					"sin": "පදිංචිය තහවුරු කිරීමේ සහතිකය",
-					"tam": "முகவரி சான்று"
-				},
-				"controlType": "fileupload",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "documentType",
-				"validators": [],
-				"required": false,
-				"transliteration": false,
-				"subType": "POA",
-				"alignmentGroup": "Documents"
-			},
-			{
-				"id": "proofOfIdentity",
-				"description": "proofOfIdentity",
-				"labelName": {
-					"eng": "Identity Proof",
-					"sin": "අනන්‍යතා තහවුරු කිරීමේ සහතිකය",
-					"tam": "அடையாளச் சான்று"
-				},
-				"controlType": "fileupload",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "documentType",
-				"validators": [],
-				"required": false,
-				"transliteration": false,
-				"subType": "POI",
-				"alignmentGroup": "Documents"
-			},
-			{
-				"id": "proofOfDateOfBirth",
-				"description": "proofOfDateOfBirth",
-				"labelName": {
-					"eng": "Date of Birth Proof",
-					"sin": "උප්පැන්න සහතිකය",
-					"tam": "பிறந்த தேதிச் சான்று"
-				},
-				"controlType": "fileupload",
-				"inputRequired": true,
-				"fieldType": "default",
-				"type": "documentType",
-				"validators": [],
-				"required": false,
-				"transliteration": false,
-				"subType": "POB",
-				"alignmentGroup": "Documents"
-			}
-		],
-		"locationHierarchy": [
-			[
-				"province",
-				"district",
-				"divisionalSecretariat",
-				"grammaNiladhari"
-			],
-			[
-				"currentProvince",
-				"currentDistrict",
-				"currentDivisionalSecretariat",
-				"currentGramaNiladhari"
-			]
-		]
-	}
+    <t>{_x000D_
+	"identity": {_x000D_
+		"identity": [_x000D_
+			{_x000D_
+				"id": "IDSchemaVersion",_x000D_
+				"description": "ID Schema Version",_x000D_
+				"type": "number",_x000D_
+				"controlType": null,_x000D_
+				"fieldType": "default",_x000D_
+				"inputRequired": false,_x000D_
+				"validators": [],_x000D_
+				"required": true_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "familyName",_x000D_
+				"description": "Family Name",_x000D_
+				"labelName": {_x000D_
+					"eng": "Family Name",_x000D_
+					"sin": "පෙළපත් නාමය",_x000D_
+					"tam": "குடும்பப் பெயர்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{3,50})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Name"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "name",_x000D_
+				"description": "Name",_x000D_
+				"labelName": {_x000D_
+					"eng": "Name",_x000D_
+					"sin": "නම",_x000D_
+					"tam": "பெயர்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{3,50}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Name"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "surname",_x000D_
+				"description": "Surname",_x000D_
+				"labelName": {_x000D_
+					"eng": "Surname",_x000D_
+					"sin": "වාසගම",_x000D_
+					"tam": "குடும்பப்பெயர்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{3,50}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Name"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "gender",_x000D_
+				"description": "gender",_x000D_
+				"labelName": {_x000D_
+					"eng": "Gender",_x000D_
+					"sin": "ස්ත්‍රී පුරුෂ භාවය",_x000D_
+					"tam": "பாலினம்"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "dynamic",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [],_x000D_
+				"required": true,_x000D_
+				"transliteration": false,_x000D_
+				"subType": "gender",_x000D_
+				"alignmentGroup": "Demographics"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "dateOfBirth",_x000D_
+				"description": "dateOfBirth",_x000D_
+				"labelName": {_x000D_
+					"eng": "Date of Birth",_x000D_
+					"sin": "උපන් දිනය",_x000D_
+					"tam": "பிறந்த தேதி"_x000D_
+				},_x000D_
+				"controlType": "ageDate",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "string",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Demographics"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "placeOfBirth",_x000D_
+				"description": "placeOfBirth",_x000D_
+				"labelName": {_x000D_
+					"eng": "Place of Birth",_x000D_
+					"sin": "උපන් ස්ථානය",_x000D_
+					"tam": "பிறந்த இடம்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{2,128}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Demographics"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "divisionalSecretariatOfBirth",_x000D_
+				"description": "divisionalSecretariatOfBirth",_x000D_
+				"labelName": {_x000D_
+					"eng": "Division",_x000D_
+					"sin": "කොට්ඨාශය",_x000D_
+					"tam": "பிறந்த பிரதேச செயலகப் பிரிவு"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{1,50}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Demographics"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "referenceIdentityNumber",_x000D_
+				"description": "referenceIdentityNumber",_x000D_
+				"labelName": {_x000D_
+					"eng": "Existing National ID Number",_x000D_
+					"sin": "පවතින ජාතික හැඳුනුම්පත් අංකය",_x000D_
+					"tam": "தற்போதைய தேசிய அடையாள அட்டை எண்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "string",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?:\\d{9}[VXvx]|\\d{12})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Identifiers"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "addressLine1",_x000D_
+				"description": "addressLine1",_x000D_
+				"labelName": {_x000D_
+					"eng": "Name or number of the House",_x000D_
+					"sin": "නිවසේ නම හෝ අංකය",_x000D_
+					"tam": "வீட்டின் பெயர் அல்லது இலக்கம்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{1,128}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Permanent Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "addressLine2",_x000D_
+				"description": "addressLine2",_x000D_
+				"labelName": {_x000D_
+					"eng": "Road/Street/Lane/Place/Garden",_x000D_
+					"sin": "පාර/වීදිය/පටුමඟ/පෙදෙස/උද්‍යානය",_x000D_
+					"tam": "வீதி/தெரு/ஒழுங்கை/இடம்/தோட்டம்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,128})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Permanent Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "addressLine3",_x000D_
+				"description": "addressLine3",_x000D_
+				"labelName": {_x000D_
+					"eng": "Village/City",_x000D_
+					"sin": "ගම/නගරය",_x000D_
+					"tam": "கிராமம்/நகரம்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,128})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Permanent Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "province",_x000D_
+				"description": "province",_x000D_
+				"labelName": {_x000D_
+					"eng": "Province",_x000D_
+					"sin": "පළාත",_x000D_
+					"tam": "மாகாணம்"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{1,50}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Permanent Address",_x000D_
+				"locationHierarchyLevel": 1,_x000D_
+				"parentLocCode": "LKA"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "district",_x000D_
+				"description": "district",_x000D_
+				"labelName": {_x000D_
+					"eng": "District",_x000D_
+					"sin": "දිස්ත්‍රික්කය",_x000D_
+					"tam": "மாவட்டம்"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{1,50}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Permanent Address",_x000D_
+				"locationHierarchyLevel": 2_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "divisionalSecretariat",_x000D_
+				"description": "divisionalSecretariat",_x000D_
+				"labelName": {_x000D_
+					"eng": "Divisional Secretariat Division",_x000D_
+					"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",_x000D_
+					"tam": "பிரதேச செயலகப் பிரிவு"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{1,50}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Permanent Address",_x000D_
+				"locationHierarchyLevel": 3_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "grammaNiladhari",_x000D_
+				"description": "grammaNiladhari",_x000D_
+				"labelName": {_x000D_
+					"eng": "Grama Niladhari Division",_x000D_
+					"sin": "ග්‍රාම නිලධාරී වසම",_x000D_
+					"tam": "கிராம அலுவலர் பிரிவு"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(?=.{1,50}$).*",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Permanent Address",_x000D_
+				"locationHierarchyLevel": 4_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "postalCode",_x000D_
+				"description": "postalCode",_x000D_
+				"labelName": {_x000D_
+					"eng": "Postal Code",_x000D_
+					"sin": "තැපැල් කේතය",_x000D_
+					"tam": "அஞ்சல் குறியீடு"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "string",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^[0-9]{5}$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": true,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Permanent Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "sameAsPermanentAddress",_x000D_
+				"description": "Same as Permanent Address Checkbox",_x000D_
+				"labelName": {_x000D_
+					"eng": "Same as Permanent Address",_x000D_
+					"sin": "ස්ථිර ලිපිනයට සමානයි",_x000D_
+					"tam": "நிரந்தர முகவரிக்கு ஒத்ததாக"_x000D_
+				},_x000D_
+				"controlType": "checkbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "boolean",_x000D_
+				"validators": [],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Current Address",_x000D_
+				"changeAction": "copy&amp;disable:addressLine1=currentAddressLine1,addressLine2=currentAddressLine2,addressLine3=currentAddressLine3,province=currentProvince,district=currentDistrict,divisionalSecretariat=currentDivisionalSecretariat,grammaNiladhari=currentGramaNiladhari,postalCode=currentPostalCode"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentAddressLine1",_x000D_
+				"description": "currentAddressLine1",_x000D_
+				"labelName": {_x000D_
+					"eng": "Name or number of the House",_x000D_
+					"sin": "නිවසේ නම හෝ අංකය",_x000D_
+					"tam": "வீட்டின் பெயர் அல்லது இலக்கம்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,128})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Current Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentAddressLine2",_x000D_
+				"description": "currentAddressLine2",_x000D_
+				"labelName": {_x000D_
+					"eng": "Road/Street/Lane/Place/Garden",_x000D_
+					"sin": "පාර/වීදිය/පටුමඟ/පෙදෙස/උද්‍යානය",_x000D_
+					"tam": "வீதி/தெரு/ஒழுங்கை/இடம்/தோட்டம்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,128})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Current Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentAddressLine3",_x000D_
+				"description": "currentAddressLine3",_x000D_
+				"labelName": {_x000D_
+					"eng": "Village/City",_x000D_
+					"sin": "ගම/නගරය",_x000D_
+					"tam": "கிராமம்/நகரம்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,128})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": true,_x000D_
+				"alignmentGroup": "Current Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentProvince",_x000D_
+				"description": "currentProvince",_x000D_
+				"labelName": {_x000D_
+					"eng": "Province",_x000D_
+					"sin": "පළාත",_x000D_
+					"tam": "மாகாணம்"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,50})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Current Address",_x000D_
+				"locationHierarchyLevel": 1,_x000D_
+				"parentLocCode": "LKA"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentDistrict",_x000D_
+				"description": "currentDistrict",_x000D_
+				"labelName": {_x000D_
+					"eng": "District",_x000D_
+					"sin": "දිස්ත්‍රික්කය",_x000D_
+					"tam": "மாவட்டம்"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,50})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Current Address",_x000D_
+				"locationHierarchyLevel": 2_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentDivisionalSecretariat",_x000D_
+				"description": "currentDivisionalSecretariat",_x000D_
+				"labelName": {_x000D_
+					"eng": "Divisional Secretariat Division",_x000D_
+					"sin": "ප්‍රාදේශීය ලේකම් කොට්ඨාශය",_x000D_
+					"tam": "பிரதேச செயலகப் பிரிவு"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,50})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Current Address",_x000D_
+				"locationHierarchyLevel": 3_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentGramaNiladhari",_x000D_
+				"description": "currentGramaNiladhari",_x000D_
+				"labelName": {_x000D_
+					"eng": "Grama Niladhari Division",_x000D_
+					"sin": "ග්‍රාම නිලධාරී වසම",_x000D_
+					"tam": "கிராம அலுவலர் பிரிவு"_x000D_
+				},_x000D_
+				"controlType": "dropdown",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "simpleType",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(|.{1,50})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Current Address",_x000D_
+				"locationHierarchyLevel": 4_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "currentPostalCode",_x000D_
+				"description": "currentPostalCode",_x000D_
+				"labelName": {_x000D_
+					"eng": "Postal Code",_x000D_
+					"sin": "තැපැල් කේතය",_x000D_
+					"tam": "அஞ்சல் குறியீடு"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "string",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^[0-9]{5}$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Current Address"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "phone",_x000D_
+				"description": "phone",_x000D_
+				"labelName": {_x000D_
+					"eng": "Phone",_x000D_
+					"sin": "දුරකථන අංකය",_x000D_
+					"tam": "தொலைபேசி"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "string",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^(0?7[0-9]{8})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Contact"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "email",_x000D_
+				"description": "email",_x000D_
+				"labelName": {_x000D_
+					"eng": "Email",_x000D_
+					"sin": "විද්‍යුත් තැපෑල",_x000D_
+					"tam": "மின்னஞ்சல்"_x000D_
+				},_x000D_
+				"controlType": "textbox",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "string",_x000D_
+				"validators": [_x000D_
+					{_x000D_
+						"type": "regex",_x000D_
+						"validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",_x000D_
+						"arguments": []_x000D_
+					}_x000D_
+				],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"alignmentGroup": "Contact"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "proofOfAddress",_x000D_
+				"description": "proofOfAddress",_x000D_
+				"labelName": {_x000D_
+					"eng": "Address Proof",_x000D_
+					"sin": "පදිංචිය තහවුරු කිරීමේ ලේඛනය",_x000D_
+					"tam": "முகவரி சான்று"_x000D_
+				},_x000D_
+				"controlType": "fileupload",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "documentType",_x000D_
+				"validators": [],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"subType": "POA",_x000D_
+				"alignmentGroup": "Documents"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "proofOfIdentity",_x000D_
+				"description": "proofOfIdentity",_x000D_
+				"labelName": {_x000D_
+					"eng": "Identity Proof",_x000D_
+					"sin": "අනන්‍යතා තහවුරු කිරීමේ ලේඛනය",_x000D_
+					"tam": "அடையாளச் சான்று"_x000D_
+				},_x000D_
+				"controlType": "fileupload",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "documentType",_x000D_
+				"validators": [],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"subType": "POI",_x000D_
+				"alignmentGroup": "Documents"_x000D_
+			},_x000D_
+			{_x000D_
+				"id": "proofOfDateOfBirth",_x000D_
+				"description": "proofOfDateOfBirth",_x000D_
+				"labelName": {_x000D_
+					"eng": "Proof of Birth Details",_x000D_
+					"sin": "උපත තහවුරු කිරීමේ ලේඛනය",_x000D_
+					"tam": "பிறப்பு உறுதிப்படுத்தல் ஆவணம்"_x000D_
+				},_x000D_
+				"controlType": "fileupload",_x000D_
+				"inputRequired": true,_x000D_
+				"fieldType": "default",_x000D_
+				"type": "documentType",_x000D_
+				"validators": [],_x000D_
+				"required": false,_x000D_
+				"transliteration": false,_x000D_
+				"subType": "POB",_x000D_
+				"alignmentGroup": "Documents"_x000D_
+			}_x000D_
+		],_x000D_
+		"locationHierarchy": [_x000D_
+			[_x000D_
+				"province",_x000D_
+				"district",_x000D_
+				"divisionalSecretariat",_x000D_
+				"grammaNiladhari"_x000D_
+			],_x000D_
+			[_x000D_
+				"currentProvince",_x000D_
+				"currentDistrict",_x000D_
+				"currentDivisionalSecretariat",_x000D_
+				"currentGramaNiladhari"_x000D_
+			]_x000D_
+		]_x000D_
+	}_x000D_
 }</t>
   </si>
 </sst>

--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>[{"name":"scheduledjobs","description":{"ara":"إعدادات الوظائف المجدولة","fra":"Paramètres des travaux planifiés","eng":"Scheduled Jobs Settings"},"label":{"ara":"إعدادات الوظائف المجدولة","fra":"Paramètres des travaux planifiés","eng":"Scheduled Jobs Settings"},"fxml":"ScheduledJobsSettings.fxml","icon":"scheduledjobs.png","order":"1","shortcut-icon":"scheduledjobs-shortcut.png","access-control":["REGISTRATION_SUPERVISOR"]},{"name":"globalconfigs","description":{"ara":"إعدادات التكوين العامة","fra":"Paramètres de configuration globale","eng":"Global Config Settings"},"label":{"ara":"إعدادات التكوين العامة","fra":"Paramètres de configuration globale","eng":"Global Config Settings"},"fxml":"GlobalConfigSettings.fxml","icon":"globalconfigs.png","order":"2","shortcut-icon":"globalconfigs-shortcut.png","access-control":["REGISTRATION_SUPERVISOR","REGISTRATION_OFFICER"]},{"name":"devices","description":{"ara":"إعدادات الجهاز","fra":"Réglages de l'appareil","eng":"Device Settings"},"label":{"ara":"إعدادات الجهاز","fra":"Réglages de l'appareil","eng":"Device Settings"},"fxml":"DeviceSettings.fxml","icon":"devices.png","order":"3","shortcut-icon":"devices-shortcut.png","access-control":["REGISTRATION_SUPERVISOR","REGISTRATION_OFFICER"]}]</t>
+          <t>[{"access-control":["REGISTRATION_SUPERVISOR"],"description":{"ara":"إعدادات الوظائف المجدولة","eng":"Scheduled Jobs Settings","fra":"Paramètres des travaux planifiés","sin":"නියමිත කාර්ය සැකසුම්","tam":"திட்டமிடப்பட்ட பணிகளின் அமைப்புகள்"},"fxml":"ScheduledJobsSettings.fxml","icon":"scheduledjobs.png","label":{"ara":"إعدادات الوظائف المجدولة","eng":"Scheduled Jobs Settings","fra":"Paramètres des travaux planifiés","sin":"නියමිත කාර්ය සැකසුම්","tam":"திட்டமிடப்பட்ட பணிகளின் அமைப்புகள்"},"name":"scheduledjobs","order":"1","shortcut-icon":"scheduledjobs-shortcut.png"},{"access-control":["REGISTRATION_SUPERVISOR","REGISTRATION_OFFICER"],"description":{"ara":"إعدادات التكوين العامة","eng":"Global Config Settings","fra":"Paramètres de configuration globale","sin":"පොදු වින්‍යාස සැකසුම්","tam":"பொது உள்ளமைவு அமைப்புகள்"},"fxml":"GlobalConfigSettings.fxml","icon":"globalconfigs.png","label":{"ara":"إعدادات التكوين العامة","eng":"Global Config Settings","fra":"Paramètres de configuration globale","sin":"පොදු වින්‍යාස සැකසුම්","tam":"பொது உள்ளமைவு அமைப்புகள்"},"name":"globalconfigs","order":"2","shortcut-icon":"globalconfigs-shortcut.png"},{"access-control":["REGISTRATION_SUPERVISOR","REGISTRATION_OFFICER"],"description":{"ara":"إعدادات الجهاز","eng":"Device Settings","fra":"Réglages de l'appareil","sin":"උපාංග සැකසුම්","tam":"சாதன அமைப்புகள்"},"fxml":"DeviceSettings.fxml","icon":"devices.png","label":{"ara":"إعدادات الجهاز","eng":"Device Settings","fra":"Réglages de l'appareil","sin":"උපාංග සැකසුම්","tam":"சாதன அமைப்புகள்"},"name":"devices","order":"3","shortcut-icon":"devices-shortcut.png"}]</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
